--- a/Results/Results.xlsx
+++ b/Results/Results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="123">
   <si>
     <t>Protocol Assessment: Compliant vs Rack&amp;Pinion</t>
   </si>
@@ -130,7 +130,7 @@
     <t>1,73 (6,95N)</t>
   </si>
   <si>
-    <t>1,88 (6,93N)</t>
+    <t>1,89 (6,93N)</t>
   </si>
   <si>
     <t>6,59 (14,65N)</t>
@@ -253,7 +253,103 @@
     <t>no adhrence without pads</t>
   </si>
   <si>
-    <t>TEST 4: TASK-LEVEL GRASPING BENCHMARK</t>
+    <t>TEST 4: DURABILITY (FATIGUE) &amp; DFMA EVALUATION</t>
+  </si>
+  <si>
+    <t>MAX VERTICALLY FORCE</t>
+  </si>
+  <si>
+    <t>Cycle No,</t>
+  </si>
+  <si>
+    <t>Max Force (N) Compliant</t>
+  </si>
+  <si>
+    <t>Max Force (N) R&amp;P</t>
+  </si>
+  <si>
+    <t>Number of 3D printed parts</t>
+  </si>
+  <si>
+    <t>Total printing time (min)</t>
+  </si>
+  <si>
+    <t>2h12</t>
+  </si>
+  <si>
+    <t>3h15m48s</t>
+  </si>
+  <si>
+    <t>Normal mode with : 15% Infill + Brim 5mm &amp; Supports : for support enforcers only</t>
+  </si>
+  <si>
+    <t>Mass of material used (g)</t>
+  </si>
+  <si>
+    <t>Printing cost (€)</t>
+  </si>
+  <si>
+    <t>(27,99/kg)</t>
+  </si>
+  <si>
+    <t>Non-printed hardware (BOM)</t>
+  </si>
+  <si>
+    <t>4x(M4x16 &amp; M4 Nuts)</t>
+  </si>
+  <si>
+    <t>2x(M6x40 Screw &amp; M6 Nuts) + 4x(M4x16 &amp; M4 Nuts)</t>
+  </si>
+  <si>
+    <t>&amp; 4 Screw for servo</t>
+  </si>
+  <si>
+    <t>Assembly time (min)</t>
+  </si>
+  <si>
+    <t>2m47</t>
+  </si>
+  <si>
+    <t>5m31</t>
+  </si>
+  <si>
+    <t>Weight (g)</t>
+  </si>
+  <si>
+    <t>50.59 (2 pieces)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.98 (7 pieces+2*M6x40+nuts) </t>
+  </si>
+  <si>
+    <t>TEST A: COMPLIANT OPTIMIZATION</t>
+  </si>
+  <si>
+    <t>Gripper ID</t>
+  </si>
+  <si>
+    <t>Max Force (N)</t>
+  </si>
+  <si>
+    <t>Peak Voltage (V)</t>
+  </si>
+  <si>
+    <t>Power (W)</t>
+  </si>
+  <si>
+    <t>Gripper 1</t>
+  </si>
+  <si>
+    <t>Gripper 2</t>
+  </si>
+  <si>
+    <t>Gripper 3</t>
+  </si>
+  <si>
+    <t>Gripper 2 with metal screw</t>
+  </si>
+  <si>
+    <t>TEST +: TASK-LEVEL GRASPING BENCHMARK</t>
   </si>
   <si>
     <t>Object Type</t>
@@ -284,103 +380,13 @@
   </si>
   <si>
     <t>Standard cube</t>
-  </si>
-  <si>
-    <t>TEST 5: DURABILITY (FATIGUE) &amp; DFMA EVALUATION</t>
-  </si>
-  <si>
-    <t>MAX VERTICALLY FORCE</t>
-  </si>
-  <si>
-    <t>Cycle No,</t>
-  </si>
-  <si>
-    <t>Max Force (N) Compliant</t>
-  </si>
-  <si>
-    <t>Max Force (N) R&amp;P</t>
-  </si>
-  <si>
-    <t>Number of 3D printed parts</t>
-  </si>
-  <si>
-    <t>Total printing time (min)</t>
-  </si>
-  <si>
-    <t>2h12</t>
-  </si>
-  <si>
-    <t>3h15m48s</t>
-  </si>
-  <si>
-    <t>Normal mode with : 15% Infill + Brim 5mm &amp; Supports : for support enforcers only</t>
-  </si>
-  <si>
-    <t>Mass of material used (g)</t>
-  </si>
-  <si>
-    <t>Printing cost (€)</t>
-  </si>
-  <si>
-    <t>(27,99/kg)</t>
-  </si>
-  <si>
-    <t>Non-printed hardware (BOM)</t>
-  </si>
-  <si>
-    <t>4x(M4x16 &amp; M4 Nuts)</t>
-  </si>
-  <si>
-    <t>2x(M6x40 Screw &amp; M6 Nuts) + 4x(M4x16 &amp; M4 Nuts)</t>
-  </si>
-  <si>
-    <t>&amp; 4 Screw for servo</t>
-  </si>
-  <si>
-    <t>Assembly time (min)</t>
-  </si>
-  <si>
-    <t>2m47</t>
-  </si>
-  <si>
-    <t>5m31</t>
-  </si>
-  <si>
-    <t>Weight (g)</t>
-  </si>
-  <si>
-    <t>TEST A: COMPLIANT OPTIMIZATION</t>
-  </si>
-  <si>
-    <t>Gripper ID</t>
-  </si>
-  <si>
-    <t>Max Force (N)</t>
-  </si>
-  <si>
-    <t>Peak Voltage (V)</t>
-  </si>
-  <si>
-    <t>Power (W)</t>
-  </si>
-  <si>
-    <t>Gripper 1</t>
-  </si>
-  <si>
-    <t>Gripper 2</t>
-  </si>
-  <si>
-    <t>Gripper 3</t>
-  </si>
-  <si>
-    <t>Gripper 2 with metal screw</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -412,6 +418,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="8">
@@ -595,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="65">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -745,6 +755,45 @@
     </xf>
     <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2170,7 +2219,7 @@
         <v>0.76</v>
       </c>
       <c r="G42" s="14">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="H42" s="14">
         <v>1.61</v>
@@ -2203,10 +2252,10 @@
         <v>1.58</v>
       </c>
       <c r="F43" s="14">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G43" s="14">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H43" s="14">
         <v>2.41</v>
@@ -2221,7 +2270,7 @@
         <v>2.38</v>
       </c>
       <c r="L43" s="14">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="44">
@@ -2386,7 +2435,7 @@
         <v>39</v>
       </c>
       <c r="G48" s="14">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="H48" s="14" t="s">
         <v>40</v>
@@ -3056,9 +3105,12 @@
     </row>
     <row r="79">
       <c r="A79" s="1"/>
-      <c r="B79" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -3067,12 +3119,9 @@
     </row>
     <row r="80">
       <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
+      <c r="B80" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -3081,24 +3130,13 @@
     </row>
     <row r="81">
       <c r="A81" s="1"/>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="1"/>
+      <c r="C81" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -3107,14 +3145,18 @@
     </row>
     <row r="82">
       <c r="A82" s="1"/>
-      <c r="B82" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C82" s="35"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="35"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="35"/>
+      <c r="B82" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -3123,14 +3165,18 @@
     </row>
     <row r="83">
       <c r="A83" s="1"/>
-      <c r="B83" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C83" s="35"/>
-      <c r="D83" s="35"/>
-      <c r="E83" s="35"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="35"/>
+      <c r="B83" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C83" s="6">
+        <v>7.48</v>
+      </c>
+      <c r="D83" s="6">
+        <v>5.74</v>
+      </c>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -3139,14 +3185,18 @@
     </row>
     <row r="84">
       <c r="A84" s="1"/>
-      <c r="B84" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" s="35"/>
-      <c r="D84" s="35"/>
-      <c r="E84" s="35"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="35"/>
+      <c r="B84" s="13">
+        <v>100.0</v>
+      </c>
+      <c r="C84" s="6">
+        <v>6.22</v>
+      </c>
+      <c r="D84" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -3155,14 +3205,18 @@
     </row>
     <row r="85">
       <c r="A85" s="1"/>
-      <c r="B85" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C85" s="35"/>
-      <c r="D85" s="35"/>
-      <c r="E85" s="35"/>
-      <c r="F85" s="35"/>
-      <c r="G85" s="35"/>
+      <c r="B85" s="13">
+        <v>200.0</v>
+      </c>
+      <c r="C85" s="6">
+        <v>7.44</v>
+      </c>
+      <c r="D85" s="6">
+        <v>5.14</v>
+      </c>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -3171,14 +3225,18 @@
     </row>
     <row r="86">
       <c r="A86" s="1"/>
-      <c r="B86" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
+      <c r="B86" s="13">
+        <v>300.0</v>
+      </c>
+      <c r="C86" s="6">
+        <v>6.72</v>
+      </c>
+      <c r="D86" s="6">
+        <v>5.16</v>
+      </c>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -3187,9 +3245,15 @@
     </row>
     <row r="87">
       <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
+      <c r="B87" s="13">
+        <v>400.0</v>
+      </c>
+      <c r="C87" s="6">
+        <v>7.1</v>
+      </c>
+      <c r="D87" s="6">
+        <v>5.08</v>
+      </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
@@ -3201,9 +3265,18 @@
     </row>
     <row r="88">
       <c r="A88" s="1"/>
-      <c r="B88" s="3" t="s">
-        <v>91</v>
-      </c>
+      <c r="B88" s="13">
+        <v>500.0</v>
+      </c>
+      <c r="C88" s="6">
+        <v>6.95</v>
+      </c>
+      <c r="D88" s="6">
+        <v>4.71</v>
+      </c>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -3213,9 +3286,8 @@
     <row r="89">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
-      <c r="C89" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
@@ -3227,15 +3299,9 @@
     </row>
     <row r="90">
       <c r="A90" s="1"/>
-      <c r="B90" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>95</v>
-      </c>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
@@ -3247,16 +3313,18 @@
     </row>
     <row r="91">
       <c r="A91" s="1"/>
-      <c r="B91" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="C91" s="6">
-        <v>7.48</v>
-      </c>
-      <c r="D91" s="6">
-        <v>5.74</v>
-      </c>
-      <c r="E91" s="1"/>
+      <c r="B91" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -3267,16 +3335,16 @@
     </row>
     <row r="92">
       <c r="A92" s="1"/>
-      <c r="B92" s="13">
-        <v>100.0</v>
+      <c r="B92" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="C92" s="6">
-        <v>6.22</v>
+        <v>2.0</v>
       </c>
       <c r="D92" s="6">
-        <v>5.2</v>
-      </c>
-      <c r="E92" s="1"/>
+        <v>7.0</v>
+      </c>
+      <c r="E92" s="35"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -3287,19 +3355,21 @@
     </row>
     <row r="93">
       <c r="A93" s="1"/>
-      <c r="B93" s="13">
-        <v>200.0</v>
-      </c>
-      <c r="C93" s="6">
-        <v>7.44</v>
-      </c>
-      <c r="D93" s="6">
-        <v>5.14</v>
-      </c>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
+      <c r="B93" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E93" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F93" s="36"/>
+      <c r="G93" s="33"/>
+      <c r="H93" s="34"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
@@ -3307,16 +3377,16 @@
     </row>
     <row r="94">
       <c r="A94" s="1"/>
-      <c r="B94" s="13">
-        <v>300.0</v>
+      <c r="B94" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="C94" s="6">
-        <v>6.72</v>
-      </c>
-      <c r="D94" s="6">
-        <v>5.16</v>
-      </c>
-      <c r="E94" s="1"/>
+        <v>54.67</v>
+      </c>
+      <c r="D94" s="37">
+        <v>52.91</v>
+      </c>
+      <c r="E94" s="35"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
@@ -3327,16 +3397,18 @@
     </row>
     <row r="95">
       <c r="A95" s="1"/>
-      <c r="B95" s="13">
-        <v>400.0</v>
+      <c r="B95" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="C95" s="6">
-        <v>7.1</v>
+        <v>1.53</v>
       </c>
       <c r="D95" s="6">
-        <v>5.08</v>
-      </c>
-      <c r="E95" s="1"/>
+        <v>1.48</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
@@ -3347,16 +3419,18 @@
     </row>
     <row r="96">
       <c r="A96" s="1"/>
-      <c r="B96" s="13">
-        <v>500.0</v>
-      </c>
-      <c r="C96" s="6">
-        <v>6.95</v>
-      </c>
-      <c r="D96" s="6">
-        <v>4.71</v>
-      </c>
-      <c r="E96" s="1"/>
+      <c r="B96" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
@@ -3367,10 +3441,16 @@
     </row>
     <row r="97">
       <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
+      <c r="B97" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C97" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D97" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="E97" s="39"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
@@ -3381,10 +3461,16 @@
     </row>
     <row r="98">
       <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
+      <c r="B98" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E98" s="27"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
@@ -3395,18 +3481,10 @@
     </row>
     <row r="99">
       <c r="A99" s="1"/>
-      <c r="B99" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -3417,19 +3495,9 @@
     </row>
     <row r="100">
       <c r="A100" s="1"/>
-      <c r="B100" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C100" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="D100" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="E100" s="35"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
+      <c r="B100" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
@@ -3437,21 +3505,13 @@
     </row>
     <row r="101">
       <c r="A101" s="1"/>
-      <c r="B101" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E101" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="F101" s="36"/>
-      <c r="G101" s="33"/>
-      <c r="H101" s="34"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
@@ -3459,19 +3519,27 @@
     </row>
     <row r="102">
       <c r="A102" s="1"/>
-      <c r="B102" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C102" s="6">
-        <v>54.67</v>
-      </c>
-      <c r="D102" s="37">
-        <v>52.91</v>
-      </c>
-      <c r="E102" s="35"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
+      <c r="B102" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
@@ -3479,21 +3547,29 @@
     </row>
     <row r="103">
       <c r="A103" s="1"/>
-      <c r="B103" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C103" s="6">
-        <v>1.53</v>
-      </c>
-      <c r="D103" s="6">
-        <v>1.48</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
+      <c r="B103" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="C103" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="D103" s="42">
+        <v>22.13</v>
+      </c>
+      <c r="E103" s="40">
+        <v>0.458</v>
+      </c>
+      <c r="F103" s="40">
+        <v>5.155</v>
+      </c>
+      <c r="G103" s="43">
+        <f t="shared" ref="G103:G117" si="9">E103*F103</f>
+        <v>2.36099</v>
+      </c>
+      <c r="H103" s="43">
+        <f t="shared" ref="H103:H117" si="10">IFERROR(D103/G103, 0)</f>
+        <v>9.373186672</v>
+      </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
@@ -3501,21 +3577,29 @@
     </row>
     <row r="104">
       <c r="A104" s="1"/>
-      <c r="B104" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
+      <c r="B104" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="C104" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="D104" s="42">
+        <v>21.53</v>
+      </c>
+      <c r="E104" s="40">
+        <v>0.462</v>
+      </c>
+      <c r="F104" s="40">
+        <v>5.098</v>
+      </c>
+      <c r="G104" s="43">
+        <f t="shared" si="9"/>
+        <v>2.355276</v>
+      </c>
+      <c r="H104" s="43">
+        <f t="shared" si="10"/>
+        <v>9.141179208</v>
+      </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
@@ -3523,19 +3607,29 @@
     </row>
     <row r="105">
       <c r="A105" s="1"/>
-      <c r="B105" s="38" t="s">
+      <c r="B105" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="C105" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="D105" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E105" s="39"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
+      <c r="C105" s="41">
+        <v>3.0</v>
+      </c>
+      <c r="D105" s="42">
+        <v>21.26</v>
+      </c>
+      <c r="E105" s="40">
+        <v>0.458</v>
+      </c>
+      <c r="F105" s="40">
+        <v>5.147</v>
+      </c>
+      <c r="G105" s="43">
+        <f t="shared" si="9"/>
+        <v>2.357326</v>
+      </c>
+      <c r="H105" s="43">
+        <f t="shared" si="10"/>
+        <v>9.018693214</v>
+      </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
@@ -3543,15 +3637,29 @@
     </row>
     <row r="106">
       <c r="A106" s="1"/>
-      <c r="B106" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C106" s="27"/>
-      <c r="D106" s="27"/>
-      <c r="E106" s="27"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
+      <c r="B106" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="C106" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="D106" s="42">
+        <v>21.21</v>
+      </c>
+      <c r="E106" s="40">
+        <v>0.458</v>
+      </c>
+      <c r="F106" s="40">
+        <v>5.138</v>
+      </c>
+      <c r="G106" s="43">
+        <f t="shared" si="9"/>
+        <v>2.353204</v>
+      </c>
+      <c r="H106" s="43">
+        <f t="shared" si="10"/>
+        <v>9.013243221</v>
+      </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
@@ -3559,13 +3667,29 @@
     </row>
     <row r="107">
       <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
+      <c r="B107" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="C107" s="41">
+        <v>5.0</v>
+      </c>
+      <c r="D107" s="42">
+        <v>21.3</v>
+      </c>
+      <c r="E107" s="40">
+        <v>0.455</v>
+      </c>
+      <c r="F107" s="40">
+        <v>5.138</v>
+      </c>
+      <c r="G107" s="43">
+        <f t="shared" si="9"/>
+        <v>2.33779</v>
+      </c>
+      <c r="H107" s="43">
+        <f t="shared" si="10"/>
+        <v>9.111169096</v>
+      </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
@@ -3573,8 +3697,28 @@
     </row>
     <row r="108">
       <c r="A108" s="1"/>
-      <c r="B108" s="3" t="s">
-        <v>112</v>
+      <c r="B108" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C108" s="45">
+        <v>1.0</v>
+      </c>
+      <c r="D108" s="46">
+        <v>27.49</v>
+      </c>
+      <c r="E108" s="44">
+        <v>0.455</v>
+      </c>
+      <c r="F108" s="44">
+        <v>5.122</v>
+      </c>
+      <c r="G108" s="47">
+        <f t="shared" si="9"/>
+        <v>2.33051</v>
+      </c>
+      <c r="H108" s="47">
+        <f t="shared" si="10"/>
+        <v>11.79570137</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -3583,13 +3727,29 @@
     </row>
     <row r="109">
       <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
+      <c r="B109" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C109" s="45">
+        <v>2.0</v>
+      </c>
+      <c r="D109" s="46">
+        <v>26.77</v>
+      </c>
+      <c r="E109" s="44">
+        <v>0.455</v>
+      </c>
+      <c r="F109" s="44">
+        <v>5.138</v>
+      </c>
+      <c r="G109" s="47">
+        <f t="shared" si="9"/>
+        <v>2.33779</v>
+      </c>
+      <c r="H109" s="47">
+        <f t="shared" si="10"/>
+        <v>11.45098576</v>
+      </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
@@ -3597,26 +3757,28 @@
     </row>
     <row r="110">
       <c r="A110" s="1"/>
-      <c r="B110" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>60</v>
+      <c r="B110" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C110" s="45">
+        <v>3.0</v>
+      </c>
+      <c r="D110" s="46">
+        <v>26.68</v>
+      </c>
+      <c r="E110" s="44">
+        <v>0.455</v>
+      </c>
+      <c r="F110" s="44">
+        <v>5.147</v>
+      </c>
+      <c r="G110" s="47">
+        <f t="shared" si="9"/>
+        <v>2.341885</v>
+      </c>
+      <c r="H110" s="47">
+        <f t="shared" si="10"/>
+        <v>11.39253208</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -3625,28 +3787,28 @@
     </row>
     <row r="111">
       <c r="A111" s="1"/>
-      <c r="B111" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C111" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="D111" s="42">
-        <v>22.13</v>
-      </c>
-      <c r="E111" s="40">
-        <v>0.458</v>
-      </c>
-      <c r="F111" s="40">
-        <v>5.155</v>
-      </c>
-      <c r="G111" s="43">
-        <f t="shared" ref="G111:G125" si="9">E111*F111</f>
-        <v>2.36099</v>
-      </c>
-      <c r="H111" s="43">
-        <f t="shared" ref="H111:H125" si="10">IFERROR(D111/G111, 0)</f>
-        <v>9.373186672</v>
+      <c r="B111" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C111" s="45">
+        <v>4.0</v>
+      </c>
+      <c r="D111" s="46">
+        <v>25.38</v>
+      </c>
+      <c r="E111" s="44">
+        <v>0.447</v>
+      </c>
+      <c r="F111" s="44">
+        <v>5.13</v>
+      </c>
+      <c r="G111" s="47">
+        <f t="shared" si="9"/>
+        <v>2.29311</v>
+      </c>
+      <c r="H111" s="47">
+        <f t="shared" si="10"/>
+        <v>11.0679383</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -3655,28 +3817,28 @@
     </row>
     <row r="112">
       <c r="A112" s="1"/>
-      <c r="B112" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C112" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="D112" s="42">
-        <v>21.53</v>
-      </c>
-      <c r="E112" s="40">
-        <v>0.462</v>
-      </c>
-      <c r="F112" s="40">
-        <v>5.098</v>
-      </c>
-      <c r="G112" s="43">
+      <c r="B112" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C112" s="45">
+        <v>5.0</v>
+      </c>
+      <c r="D112" s="46">
+        <v>25.77</v>
+      </c>
+      <c r="E112" s="44">
+        <v>0.451</v>
+      </c>
+      <c r="F112" s="44">
+        <v>5.138</v>
+      </c>
+      <c r="G112" s="47">
         <f t="shared" si="9"/>
-        <v>2.355276</v>
-      </c>
-      <c r="H112" s="43">
+        <v>2.317238</v>
+      </c>
+      <c r="H112" s="47">
         <f t="shared" si="10"/>
-        <v>9.141179208</v>
+        <v>11.12099836</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -3685,28 +3847,28 @@
     </row>
     <row r="113">
       <c r="A113" s="1"/>
-      <c r="B113" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C113" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="D113" s="42">
-        <v>21.26</v>
-      </c>
-      <c r="E113" s="40">
+      <c r="B113" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C113" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D113" s="50">
+        <v>25.79</v>
+      </c>
+      <c r="E113" s="48">
         <v>0.458</v>
       </c>
-      <c r="F113" s="40">
-        <v>5.147</v>
-      </c>
-      <c r="G113" s="43">
+      <c r="F113" s="48">
+        <v>5.13</v>
+      </c>
+      <c r="G113" s="51">
         <f t="shared" si="9"/>
-        <v>2.357326</v>
-      </c>
-      <c r="H113" s="43">
+        <v>2.34954</v>
+      </c>
+      <c r="H113" s="51">
         <f t="shared" si="10"/>
-        <v>9.018693214</v>
+        <v>10.9766167</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -3715,28 +3877,28 @@
     </row>
     <row r="114">
       <c r="A114" s="1"/>
-      <c r="B114" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C114" s="41">
-        <v>4.0</v>
-      </c>
-      <c r="D114" s="42">
-        <v>21.21</v>
-      </c>
-      <c r="E114" s="40">
-        <v>0.458</v>
-      </c>
-      <c r="F114" s="40">
+      <c r="B114" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C114" s="49">
+        <v>2.0</v>
+      </c>
+      <c r="D114" s="50">
+        <v>23.58</v>
+      </c>
+      <c r="E114" s="48">
+        <v>0.455</v>
+      </c>
+      <c r="F114" s="48">
         <v>5.138</v>
       </c>
-      <c r="G114" s="43">
+      <c r="G114" s="51">
         <f t="shared" si="9"/>
-        <v>2.353204</v>
-      </c>
-      <c r="H114" s="43">
+        <v>2.33779</v>
+      </c>
+      <c r="H114" s="51">
         <f t="shared" si="10"/>
-        <v>9.013243221</v>
+        <v>10.08644917</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -3745,28 +3907,28 @@
     </row>
     <row r="115">
       <c r="A115" s="1"/>
-      <c r="B115" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C115" s="41">
-        <v>5.0</v>
-      </c>
-      <c r="D115" s="42">
-        <v>21.3</v>
-      </c>
-      <c r="E115" s="40">
-        <v>0.455</v>
-      </c>
-      <c r="F115" s="40">
+      <c r="B115" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C115" s="49">
+        <v>3.0</v>
+      </c>
+      <c r="D115" s="50">
+        <v>25.71</v>
+      </c>
+      <c r="E115" s="48">
+        <v>0.451</v>
+      </c>
+      <c r="F115" s="48">
         <v>5.138</v>
       </c>
-      <c r="G115" s="43">
+      <c r="G115" s="51">
         <f t="shared" si="9"/>
-        <v>2.33779</v>
-      </c>
-      <c r="H115" s="43">
+        <v>2.317238</v>
+      </c>
+      <c r="H115" s="51">
         <f t="shared" si="10"/>
-        <v>9.111169096</v>
+        <v>11.09510547</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -3775,28 +3937,28 @@
     </row>
     <row r="116">
       <c r="A116" s="1"/>
-      <c r="B116" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C116" s="45">
-        <v>1.0</v>
-      </c>
-      <c r="D116" s="46">
-        <v>27.49</v>
-      </c>
-      <c r="E116" s="44">
-        <v>0.455</v>
-      </c>
-      <c r="F116" s="44">
+      <c r="B116" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C116" s="49">
+        <v>4.0</v>
+      </c>
+      <c r="D116" s="50">
+        <v>25.62</v>
+      </c>
+      <c r="E116" s="48">
+        <v>0.458</v>
+      </c>
+      <c r="F116" s="48">
         <v>5.122</v>
       </c>
-      <c r="G116" s="47">
+      <c r="G116" s="51">
         <f t="shared" si="9"/>
-        <v>2.33051</v>
-      </c>
-      <c r="H116" s="47">
+        <v>2.345876</v>
+      </c>
+      <c r="H116" s="51">
         <f t="shared" si="10"/>
-        <v>11.79570137</v>
+        <v>10.92129337</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -3805,28 +3967,28 @@
     </row>
     <row r="117">
       <c r="A117" s="1"/>
-      <c r="B117" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C117" s="45">
-        <v>2.0</v>
-      </c>
-      <c r="D117" s="46">
-        <v>26.77</v>
-      </c>
-      <c r="E117" s="44">
+      <c r="B117" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C117" s="49">
+        <v>5.0</v>
+      </c>
+      <c r="D117" s="50">
+        <v>25.71</v>
+      </c>
+      <c r="E117" s="48">
         <v>0.455</v>
       </c>
-      <c r="F117" s="44">
+      <c r="F117" s="48">
         <v>5.138</v>
       </c>
-      <c r="G117" s="47">
+      <c r="G117" s="51">
         <f t="shared" si="9"/>
         <v>2.33779</v>
       </c>
-      <c r="H117" s="47">
+      <c r="H117" s="51">
         <f t="shared" si="10"/>
-        <v>11.45098576</v>
+        <v>10.99756608</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -3835,29 +3997,13 @@
     </row>
     <row r="118">
       <c r="A118" s="1"/>
-      <c r="B118" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C118" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="D118" s="46">
-        <v>26.68</v>
-      </c>
-      <c r="E118" s="44">
-        <v>0.455</v>
-      </c>
-      <c r="F118" s="44">
-        <v>5.147</v>
-      </c>
-      <c r="G118" s="47">
-        <f t="shared" si="9"/>
-        <v>2.341885</v>
-      </c>
-      <c r="H118" s="47">
-        <f t="shared" si="10"/>
-        <v>11.39253208</v>
-      </c>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
@@ -3865,29 +4011,13 @@
     </row>
     <row r="119">
       <c r="A119" s="1"/>
-      <c r="B119" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C119" s="45">
-        <v>4.0</v>
-      </c>
-      <c r="D119" s="46">
-        <v>25.38</v>
-      </c>
-      <c r="E119" s="44">
-        <v>0.447</v>
-      </c>
-      <c r="F119" s="44">
-        <v>5.13</v>
-      </c>
-      <c r="G119" s="47">
-        <f t="shared" si="9"/>
-        <v>2.29311</v>
-      </c>
-      <c r="H119" s="47">
-        <f t="shared" si="10"/>
-        <v>11.0679383</v>
-      </c>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
@@ -3896,27 +4026,27 @@
     <row r="120">
       <c r="A120" s="1"/>
       <c r="B120" s="44" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C120" s="45">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="D120" s="46">
-        <v>25.77</v>
+        <v>33.23</v>
       </c>
       <c r="E120" s="44">
-        <v>0.451</v>
+        <v>0.431</v>
       </c>
       <c r="F120" s="44">
         <v>5.138</v>
       </c>
       <c r="G120" s="47">
-        <f t="shared" si="9"/>
-        <v>2.317238</v>
+        <f t="shared" ref="G120:G124" si="11">E120*F120</f>
+        <v>2.214478</v>
       </c>
       <c r="H120" s="47">
-        <f t="shared" si="10"/>
-        <v>11.12099836</v>
+        <f t="shared" ref="H120:H124" si="12">IFERROR(D120/G120, 0)</f>
+        <v>15.00579369</v>
       </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
@@ -3925,28 +4055,28 @@
     </row>
     <row r="121">
       <c r="A121" s="1"/>
-      <c r="B121" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="C121" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D121" s="50">
-        <v>25.79</v>
-      </c>
-      <c r="E121" s="48">
-        <v>0.458</v>
-      </c>
-      <c r="F121" s="48">
-        <v>5.13</v>
-      </c>
-      <c r="G121" s="51">
-        <f t="shared" si="9"/>
-        <v>2.34954</v>
-      </c>
-      <c r="H121" s="51">
-        <f t="shared" si="10"/>
-        <v>10.9766167</v>
+      <c r="B121" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C121" s="45">
+        <v>2.0</v>
+      </c>
+      <c r="D121" s="46">
+        <v>31.86</v>
+      </c>
+      <c r="E121" s="44">
+        <v>0.435</v>
+      </c>
+      <c r="F121" s="44">
+        <v>5.138</v>
+      </c>
+      <c r="G121" s="47">
+        <f t="shared" si="11"/>
+        <v>2.23503</v>
+      </c>
+      <c r="H121" s="47">
+        <f t="shared" si="12"/>
+        <v>14.25484222</v>
       </c>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
@@ -3955,28 +4085,28 @@
     </row>
     <row r="122">
       <c r="A122" s="1"/>
-      <c r="B122" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="C122" s="49">
-        <v>2.0</v>
-      </c>
-      <c r="D122" s="50">
-        <v>23.58</v>
-      </c>
-      <c r="E122" s="48">
-        <v>0.455</v>
-      </c>
-      <c r="F122" s="48">
-        <v>5.138</v>
-      </c>
-      <c r="G122" s="51">
-        <f t="shared" si="9"/>
-        <v>2.33779</v>
-      </c>
-      <c r="H122" s="51">
-        <f t="shared" si="10"/>
-        <v>10.08644917</v>
+      <c r="B122" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C122" s="45">
+        <v>3.0</v>
+      </c>
+      <c r="D122" s="46">
+        <v>31.96</v>
+      </c>
+      <c r="E122" s="44">
+        <v>0.431</v>
+      </c>
+      <c r="F122" s="44">
+        <v>5.163</v>
+      </c>
+      <c r="G122" s="47">
+        <f t="shared" si="11"/>
+        <v>2.225253</v>
+      </c>
+      <c r="H122" s="47">
+        <f t="shared" si="12"/>
+        <v>14.36241182</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
@@ -3985,28 +4115,28 @@
     </row>
     <row r="123">
       <c r="A123" s="1"/>
-      <c r="B123" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="C123" s="49">
-        <v>3.0</v>
-      </c>
-      <c r="D123" s="50">
-        <v>25.71</v>
-      </c>
-      <c r="E123" s="48">
-        <v>0.451</v>
-      </c>
-      <c r="F123" s="48">
-        <v>5.138</v>
-      </c>
-      <c r="G123" s="51">
-        <f t="shared" si="9"/>
-        <v>2.317238</v>
-      </c>
-      <c r="H123" s="51">
-        <f t="shared" si="10"/>
-        <v>11.09510547</v>
+      <c r="B123" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C123" s="45">
+        <v>4.0</v>
+      </c>
+      <c r="D123" s="46">
+        <v>32.51</v>
+      </c>
+      <c r="E123" s="44">
+        <v>0.415</v>
+      </c>
+      <c r="F123" s="44">
+        <v>5.155</v>
+      </c>
+      <c r="G123" s="47">
+        <f t="shared" si="11"/>
+        <v>2.139325</v>
+      </c>
+      <c r="H123" s="47">
+        <f t="shared" si="12"/>
+        <v>15.19638204</v>
       </c>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
@@ -4015,28 +4145,28 @@
     </row>
     <row r="124">
       <c r="A124" s="1"/>
-      <c r="B124" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="C124" s="49">
-        <v>4.0</v>
-      </c>
-      <c r="D124" s="50">
-        <v>25.62</v>
-      </c>
-      <c r="E124" s="48">
-        <v>0.458</v>
-      </c>
-      <c r="F124" s="48">
-        <v>5.122</v>
-      </c>
-      <c r="G124" s="51">
-        <f t="shared" si="9"/>
-        <v>2.345876</v>
-      </c>
-      <c r="H124" s="51">
-        <f t="shared" si="10"/>
-        <v>10.92129337</v>
+      <c r="B124" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C124" s="45">
+        <v>5.0</v>
+      </c>
+      <c r="D124" s="46">
+        <v>26.66</v>
+      </c>
+      <c r="E124" s="44">
+        <v>0.439</v>
+      </c>
+      <c r="F124" s="44">
+        <v>5.163</v>
+      </c>
+      <c r="G124" s="47">
+        <f t="shared" si="11"/>
+        <v>2.266557</v>
+      </c>
+      <c r="H124" s="47">
+        <f t="shared" si="12"/>
+        <v>11.7623338</v>
       </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
@@ -4045,29 +4175,13 @@
     </row>
     <row r="125">
       <c r="A125" s="1"/>
-      <c r="B125" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="C125" s="49">
-        <v>5.0</v>
-      </c>
-      <c r="D125" s="50">
-        <v>25.71</v>
-      </c>
-      <c r="E125" s="48">
-        <v>0.455</v>
-      </c>
-      <c r="F125" s="48">
-        <v>5.138</v>
-      </c>
-      <c r="G125" s="51">
-        <f t="shared" si="9"/>
-        <v>2.33779</v>
-      </c>
-      <c r="H125" s="51">
-        <f t="shared" si="10"/>
-        <v>10.99756608</v>
-      </c>
+      <c r="B125" s="34"/>
+      <c r="C125" s="52"/>
+      <c r="D125" s="53"/>
+      <c r="E125" s="34"/>
+      <c r="F125" s="34"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1"/>
@@ -4075,11 +4189,11 @@
     </row>
     <row r="126">
       <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
+      <c r="B126" s="34"/>
+      <c r="C126" s="52"/>
+      <c r="D126" s="53"/>
+      <c r="E126" s="34"/>
+      <c r="F126" s="34"/>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
@@ -4089,11 +4203,11 @@
     </row>
     <row r="127">
       <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="52"/>
+      <c r="D127" s="53"/>
+      <c r="E127" s="34"/>
+      <c r="F127" s="34"/>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -4103,29 +4217,13 @@
     </row>
     <row r="128">
       <c r="A128" s="1"/>
-      <c r="B128" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="C128" s="45">
-        <v>1.0</v>
-      </c>
-      <c r="D128" s="46">
-        <v>33.23</v>
-      </c>
-      <c r="E128" s="44">
-        <v>0.431</v>
-      </c>
-      <c r="F128" s="44">
-        <v>5.138</v>
-      </c>
-      <c r="G128" s="47">
-        <f t="shared" ref="G128:G132" si="11">E128*F128</f>
-        <v>2.214478</v>
-      </c>
-      <c r="H128" s="47">
-        <f t="shared" ref="H128:H132" si="12">IFERROR(D128/G128, 0)</f>
-        <v>15.00579369</v>
-      </c>
+      <c r="B128" s="34"/>
+      <c r="C128" s="52"/>
+      <c r="D128" s="53"/>
+      <c r="E128" s="34"/>
+      <c r="F128" s="34"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
@@ -4133,29 +4231,10 @@
     </row>
     <row r="129">
       <c r="A129" s="1"/>
-      <c r="B129" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="C129" s="45">
-        <v>2.0</v>
-      </c>
-      <c r="D129" s="46">
-        <v>31.86</v>
-      </c>
-      <c r="E129" s="44">
-        <v>0.435</v>
-      </c>
-      <c r="F129" s="44">
-        <v>5.138</v>
-      </c>
-      <c r="G129" s="47">
-        <f t="shared" si="11"/>
-        <v>2.23503</v>
-      </c>
-      <c r="H129" s="47">
-        <f t="shared" si="12"/>
-        <v>14.25484222</v>
-      </c>
+      <c r="B129" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="H129" s="1"/>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
@@ -4163,29 +4242,13 @@
     </row>
     <row r="130">
       <c r="A130" s="1"/>
-      <c r="B130" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="C130" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="D130" s="46">
-        <v>31.96</v>
-      </c>
-      <c r="E130" s="44">
-        <v>0.431</v>
-      </c>
-      <c r="F130" s="44">
-        <v>5.163</v>
-      </c>
-      <c r="G130" s="47">
-        <f t="shared" si="11"/>
-        <v>2.225253</v>
-      </c>
-      <c r="H130" s="47">
-        <f t="shared" si="12"/>
-        <v>14.36241182</v>
-      </c>
+      <c r="B130" s="55"/>
+      <c r="C130" s="56"/>
+      <c r="D130" s="57"/>
+      <c r="E130" s="55"/>
+      <c r="F130" s="55"/>
+      <c r="G130" s="56"/>
+      <c r="H130" s="1"/>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
@@ -4193,29 +4256,25 @@
     </row>
     <row r="131">
       <c r="A131" s="1"/>
-      <c r="B131" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="C131" s="45">
-        <v>4.0</v>
-      </c>
-      <c r="D131" s="46">
-        <v>32.51</v>
-      </c>
-      <c r="E131" s="44">
-        <v>0.415</v>
-      </c>
-      <c r="F131" s="44">
-        <v>5.155</v>
-      </c>
-      <c r="G131" s="47">
-        <f t="shared" si="11"/>
-        <v>2.139325</v>
-      </c>
-      <c r="H131" s="47">
-        <f t="shared" si="12"/>
-        <v>15.19638204</v>
-      </c>
+      <c r="B131" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="C131" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="D131" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="E131" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="F131" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="G131" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="H131" s="1"/>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
       <c r="K131" s="1"/>
@@ -4223,44 +4282,1318 @@
     </row>
     <row r="132">
       <c r="A132" s="1"/>
-      <c r="B132" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="C132" s="45">
-        <v>5.0</v>
-      </c>
-      <c r="D132" s="46">
-        <v>26.66</v>
-      </c>
-      <c r="E132" s="44">
-        <v>0.439</v>
-      </c>
-      <c r="F132" s="44">
-        <v>5.163</v>
-      </c>
-      <c r="G132" s="47">
-        <f t="shared" si="11"/>
-        <v>2.266557</v>
-      </c>
-      <c r="H132" s="47">
-        <f t="shared" si="12"/>
-        <v>11.7623338</v>
-      </c>
+      <c r="B132" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="C132" s="62"/>
+      <c r="D132" s="63"/>
+      <c r="E132" s="64"/>
+      <c r="F132" s="64"/>
+      <c r="G132" s="62"/>
+      <c r="H132" s="1"/>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
       <c r="L132" s="1"/>
     </row>
+    <row r="133">
+      <c r="A133" s="1"/>
+      <c r="B133" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="C133" s="62"/>
+      <c r="D133" s="63"/>
+      <c r="E133" s="64"/>
+      <c r="F133" s="64"/>
+      <c r="G133" s="62"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
+      <c r="K133" s="1"/>
+      <c r="L133" s="1"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1"/>
+      <c r="B134" s="61" t="s">
+        <v>120</v>
+      </c>
+      <c r="C134" s="62"/>
+      <c r="D134" s="63"/>
+      <c r="E134" s="64"/>
+      <c r="F134" s="64"/>
+      <c r="G134" s="62"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+      <c r="L134" s="1"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1"/>
+      <c r="B135" s="61" t="s">
+        <v>121</v>
+      </c>
+      <c r="C135" s="62"/>
+      <c r="D135" s="63"/>
+      <c r="E135" s="64"/>
+      <c r="F135" s="64"/>
+      <c r="G135" s="62"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1"/>
+      <c r="K135" s="1"/>
+      <c r="L135" s="1"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1"/>
+      <c r="B136" s="61" t="s">
+        <v>122</v>
+      </c>
+      <c r="C136" s="62"/>
+      <c r="D136" s="63"/>
+      <c r="E136" s="64"/>
+      <c r="F136" s="64"/>
+      <c r="G136" s="62"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1"/>
+      <c r="B137" s="34"/>
+      <c r="C137" s="52"/>
+      <c r="D137" s="53"/>
+      <c r="E137" s="34"/>
+      <c r="F137" s="34"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+      <c r="K137" s="1"/>
+      <c r="L137" s="1"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1"/>
+      <c r="B138" s="34"/>
+      <c r="C138" s="52"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="34"/>
+      <c r="F138" s="34"/>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
+      <c r="K138" s="1"/>
+      <c r="L138" s="1"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="52"/>
+      <c r="D139" s="53"/>
+      <c r="E139" s="34"/>
+      <c r="F139" s="34"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
+      <c r="K139" s="1"/>
+      <c r="L139" s="1"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1"/>
+      <c r="B140" s="34"/>
+      <c r="C140" s="52"/>
+      <c r="D140" s="53"/>
+      <c r="E140" s="34"/>
+      <c r="F140" s="34"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
+      <c r="K140" s="1"/>
+      <c r="L140" s="1"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1"/>
+      <c r="B141" s="34"/>
+      <c r="C141" s="52"/>
+      <c r="D141" s="53"/>
+      <c r="E141" s="34"/>
+      <c r="F141" s="34"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1"/>
+      <c r="K141" s="1"/>
+      <c r="L141" s="1"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1"/>
+      <c r="B142" s="34"/>
+      <c r="C142" s="52"/>
+      <c r="D142" s="53"/>
+      <c r="E142" s="34"/>
+      <c r="F142" s="34"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
+      <c r="K142" s="1"/>
+      <c r="L142" s="1"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1"/>
+      <c r="B143" s="34"/>
+      <c r="C143" s="52"/>
+      <c r="D143" s="53"/>
+      <c r="E143" s="34"/>
+      <c r="F143" s="34"/>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
+      <c r="K143" s="1"/>
+      <c r="L143" s="1"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1"/>
+      <c r="B144" s="34"/>
+      <c r="C144" s="52"/>
+      <c r="D144" s="53"/>
+      <c r="E144" s="34"/>
+      <c r="F144" s="34"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
+      <c r="K144" s="1"/>
+      <c r="L144" s="1"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="52"/>
+      <c r="D145" s="53"/>
+      <c r="E145" s="34"/>
+      <c r="F145" s="34"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
+      <c r="K145" s="1"/>
+      <c r="L145" s="1"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1"/>
+      <c r="B146" s="34"/>
+      <c r="C146" s="52"/>
+      <c r="D146" s="53"/>
+      <c r="E146" s="34"/>
+      <c r="F146" s="34"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
+      <c r="K146" s="1"/>
+      <c r="L146" s="1"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="1"/>
+      <c r="B147" s="34"/>
+      <c r="C147" s="52"/>
+      <c r="D147" s="53"/>
+      <c r="E147" s="34"/>
+      <c r="F147" s="34"/>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1"/>
+      <c r="K147" s="1"/>
+      <c r="L147" s="1"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1"/>
+      <c r="B148" s="34"/>
+      <c r="C148" s="52"/>
+      <c r="D148" s="53"/>
+      <c r="E148" s="34"/>
+      <c r="F148" s="34"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
+      <c r="K148" s="1"/>
+      <c r="L148" s="1"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="1"/>
+      <c r="B149" s="34"/>
+      <c r="C149" s="52"/>
+      <c r="D149" s="53"/>
+      <c r="E149" s="34"/>
+      <c r="F149" s="34"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
+      <c r="K149" s="1"/>
+      <c r="L149" s="1"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="1"/>
+      <c r="B150" s="34"/>
+      <c r="C150" s="52"/>
+      <c r="D150" s="53"/>
+      <c r="E150" s="34"/>
+      <c r="F150" s="34"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
+      <c r="K150" s="1"/>
+      <c r="L150" s="1"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="52"/>
+      <c r="D151" s="53"/>
+      <c r="E151" s="34"/>
+      <c r="F151" s="34"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
+      <c r="K151" s="1"/>
+      <c r="L151" s="1"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1"/>
+      <c r="B152" s="34"/>
+      <c r="C152" s="52"/>
+      <c r="D152" s="53"/>
+      <c r="E152" s="34"/>
+      <c r="F152" s="34"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
+      <c r="K152" s="1"/>
+      <c r="L152" s="1"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1"/>
+      <c r="B153" s="34"/>
+      <c r="C153" s="52"/>
+      <c r="D153" s="53"/>
+      <c r="E153" s="34"/>
+      <c r="F153" s="34"/>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
+      <c r="K153" s="1"/>
+      <c r="L153" s="1"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1"/>
+      <c r="B154" s="34"/>
+      <c r="C154" s="52"/>
+      <c r="D154" s="53"/>
+      <c r="E154" s="34"/>
+      <c r="F154" s="34"/>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+      <c r="J154" s="1"/>
+      <c r="K154" s="1"/>
+      <c r="L154" s="1"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1"/>
+      <c r="B155" s="34"/>
+      <c r="C155" s="52"/>
+      <c r="D155" s="53"/>
+      <c r="E155" s="34"/>
+      <c r="F155" s="34"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1"/>
+      <c r="K155" s="1"/>
+      <c r="L155" s="1"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1"/>
+      <c r="B156" s="34"/>
+      <c r="C156" s="52"/>
+      <c r="D156" s="53"/>
+      <c r="E156" s="34"/>
+      <c r="F156" s="34"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
+      <c r="K156" s="1"/>
+      <c r="L156" s="1"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="52"/>
+      <c r="D157" s="53"/>
+      <c r="E157" s="34"/>
+      <c r="F157" s="34"/>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1"/>
+      <c r="K157" s="1"/>
+      <c r="L157" s="1"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1"/>
+      <c r="B158" s="34"/>
+      <c r="C158" s="52"/>
+      <c r="D158" s="53"/>
+      <c r="E158" s="34"/>
+      <c r="F158" s="34"/>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+      <c r="J158" s="1"/>
+      <c r="K158" s="1"/>
+      <c r="L158" s="1"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="1"/>
+      <c r="B159" s="34"/>
+      <c r="C159" s="52"/>
+      <c r="D159" s="53"/>
+      <c r="E159" s="34"/>
+      <c r="F159" s="34"/>
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="1"/>
+      <c r="J159" s="1"/>
+      <c r="K159" s="1"/>
+      <c r="L159" s="1"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1"/>
+      <c r="B160" s="34"/>
+      <c r="C160" s="52"/>
+      <c r="D160" s="53"/>
+      <c r="E160" s="34"/>
+      <c r="F160" s="34"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1"/>
+      <c r="B161" s="34"/>
+      <c r="C161" s="52"/>
+      <c r="D161" s="53"/>
+      <c r="E161" s="34"/>
+      <c r="F161" s="34"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+      <c r="L161" s="1"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="1"/>
+      <c r="B162" s="34"/>
+      <c r="C162" s="52"/>
+      <c r="D162" s="53"/>
+      <c r="E162" s="34"/>
+      <c r="F162" s="34"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+      <c r="J162" s="1"/>
+      <c r="K162" s="1"/>
+      <c r="L162" s="1"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1"/>
+      <c r="B163" s="34"/>
+      <c r="C163" s="52"/>
+      <c r="D163" s="53"/>
+      <c r="E163" s="34"/>
+      <c r="F163" s="34"/>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="1"/>
+      <c r="J163" s="1"/>
+      <c r="K163" s="1"/>
+      <c r="L163" s="1"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1"/>
+      <c r="B164" s="34"/>
+      <c r="C164" s="52"/>
+      <c r="D164" s="53"/>
+      <c r="E164" s="34"/>
+      <c r="F164" s="34"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+      <c r="J164" s="1"/>
+      <c r="K164" s="1"/>
+      <c r="L164" s="1"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1"/>
+      <c r="B165" s="34"/>
+      <c r="C165" s="52"/>
+      <c r="D165" s="53"/>
+      <c r="E165" s="34"/>
+      <c r="F165" s="34"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="J165" s="1"/>
+      <c r="K165" s="1"/>
+      <c r="L165" s="1"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1"/>
+      <c r="B166" s="34"/>
+      <c r="C166" s="52"/>
+      <c r="D166" s="53"/>
+      <c r="E166" s="34"/>
+      <c r="F166" s="34"/>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+      <c r="J166" s="1"/>
+      <c r="K166" s="1"/>
+      <c r="L166" s="1"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1"/>
+      <c r="B167" s="34"/>
+      <c r="C167" s="52"/>
+      <c r="D167" s="53"/>
+      <c r="E167" s="34"/>
+      <c r="F167" s="34"/>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+      <c r="J167" s="1"/>
+      <c r="K167" s="1"/>
+      <c r="L167" s="1"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1"/>
+      <c r="B168" s="34"/>
+      <c r="C168" s="52"/>
+      <c r="D168" s="53"/>
+      <c r="E168" s="34"/>
+      <c r="F168" s="34"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+      <c r="J168" s="1"/>
+      <c r="K168" s="1"/>
+      <c r="L168" s="1"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="1"/>
+      <c r="B169" s="34"/>
+      <c r="C169" s="52"/>
+      <c r="D169" s="53"/>
+      <c r="E169" s="34"/>
+      <c r="F169" s="34"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1"/>
+      <c r="L169" s="1"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1"/>
+      <c r="B170" s="34"/>
+      <c r="C170" s="52"/>
+      <c r="D170" s="53"/>
+      <c r="E170" s="34"/>
+      <c r="F170" s="34"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+      <c r="K170" s="1"/>
+      <c r="L170" s="1"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1"/>
+      <c r="B171" s="34"/>
+      <c r="C171" s="52"/>
+      <c r="D171" s="53"/>
+      <c r="E171" s="34"/>
+      <c r="F171" s="34"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+      <c r="K171" s="1"/>
+      <c r="L171" s="1"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1"/>
+      <c r="B172" s="34"/>
+      <c r="C172" s="52"/>
+      <c r="D172" s="53"/>
+      <c r="E172" s="34"/>
+      <c r="F172" s="34"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+      <c r="K172" s="1"/>
+      <c r="L172" s="1"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1"/>
+      <c r="B173" s="34"/>
+      <c r="C173" s="52"/>
+      <c r="D173" s="53"/>
+      <c r="E173" s="34"/>
+      <c r="F173" s="34"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+      <c r="K173" s="1"/>
+      <c r="L173" s="1"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1"/>
+      <c r="B174" s="34"/>
+      <c r="C174" s="52"/>
+      <c r="D174" s="53"/>
+      <c r="E174" s="34"/>
+      <c r="F174" s="34"/>
+      <c r="G174" s="1"/>
+      <c r="H174" s="1"/>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+      <c r="K174" s="1"/>
+      <c r="L174" s="1"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1"/>
+      <c r="B175" s="34"/>
+      <c r="C175" s="52"/>
+      <c r="D175" s="53"/>
+      <c r="E175" s="34"/>
+      <c r="F175" s="34"/>
+      <c r="G175" s="1"/>
+      <c r="H175" s="1"/>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
+      <c r="L175" s="1"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1"/>
+      <c r="B176" s="34"/>
+      <c r="C176" s="52"/>
+      <c r="D176" s="53"/>
+      <c r="E176" s="34"/>
+      <c r="F176" s="34"/>
+      <c r="G176" s="1"/>
+      <c r="H176" s="1"/>
+      <c r="I176" s="1"/>
+      <c r="J176" s="1"/>
+      <c r="K176" s="1"/>
+      <c r="L176" s="1"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1"/>
+      <c r="B177" s="34"/>
+      <c r="C177" s="52"/>
+      <c r="D177" s="53"/>
+      <c r="E177" s="34"/>
+      <c r="F177" s="34"/>
+      <c r="G177" s="1"/>
+      <c r="H177" s="1"/>
+      <c r="I177" s="1"/>
+      <c r="J177" s="1"/>
+      <c r="K177" s="1"/>
+      <c r="L177" s="1"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1"/>
+      <c r="B178" s="34"/>
+      <c r="C178" s="52"/>
+      <c r="D178" s="53"/>
+      <c r="E178" s="34"/>
+      <c r="F178" s="34"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+      <c r="J178" s="1"/>
+      <c r="K178" s="1"/>
+      <c r="L178" s="1"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1"/>
+      <c r="B179" s="34"/>
+      <c r="C179" s="52"/>
+      <c r="D179" s="53"/>
+      <c r="E179" s="34"/>
+      <c r="F179" s="34"/>
+      <c r="G179" s="1"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
+      <c r="J179" s="1"/>
+      <c r="K179" s="1"/>
+      <c r="L179" s="1"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1"/>
+      <c r="B180" s="34"/>
+      <c r="C180" s="52"/>
+      <c r="D180" s="53"/>
+      <c r="E180" s="34"/>
+      <c r="F180" s="34"/>
+      <c r="G180" s="1"/>
+      <c r="H180" s="1"/>
+      <c r="I180" s="1"/>
+      <c r="J180" s="1"/>
+      <c r="K180" s="1"/>
+      <c r="L180" s="1"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1"/>
+      <c r="B181" s="34"/>
+      <c r="C181" s="52"/>
+      <c r="D181" s="53"/>
+      <c r="E181" s="34"/>
+      <c r="F181" s="34"/>
+      <c r="G181" s="1"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+      <c r="J181" s="1"/>
+      <c r="K181" s="1"/>
+      <c r="L181" s="1"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1"/>
+      <c r="B182" s="34"/>
+      <c r="C182" s="52"/>
+      <c r="D182" s="53"/>
+      <c r="E182" s="34"/>
+      <c r="F182" s="34"/>
+      <c r="G182" s="1"/>
+      <c r="H182" s="1"/>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
+      <c r="K182" s="1"/>
+      <c r="L182" s="1"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1"/>
+      <c r="B183" s="34"/>
+      <c r="C183" s="52"/>
+      <c r="D183" s="53"/>
+      <c r="E183" s="34"/>
+      <c r="F183" s="34"/>
+      <c r="G183" s="1"/>
+      <c r="H183" s="1"/>
+      <c r="I183" s="1"/>
+      <c r="J183" s="1"/>
+      <c r="K183" s="1"/>
+      <c r="L183" s="1"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1"/>
+      <c r="B184" s="34"/>
+      <c r="C184" s="52"/>
+      <c r="D184" s="53"/>
+      <c r="E184" s="34"/>
+      <c r="F184" s="34"/>
+      <c r="G184" s="1"/>
+      <c r="H184" s="1"/>
+      <c r="I184" s="1"/>
+      <c r="J184" s="1"/>
+      <c r="K184" s="1"/>
+      <c r="L184" s="1"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1"/>
+      <c r="B185" s="34"/>
+      <c r="C185" s="52"/>
+      <c r="D185" s="53"/>
+      <c r="E185" s="34"/>
+      <c r="F185" s="34"/>
+      <c r="G185" s="1"/>
+      <c r="H185" s="1"/>
+      <c r="I185" s="1"/>
+      <c r="J185" s="1"/>
+      <c r="K185" s="1"/>
+      <c r="L185" s="1"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1"/>
+      <c r="B186" s="34"/>
+      <c r="C186" s="52"/>
+      <c r="D186" s="53"/>
+      <c r="E186" s="34"/>
+      <c r="F186" s="34"/>
+      <c r="G186" s="1"/>
+      <c r="H186" s="1"/>
+      <c r="I186" s="1"/>
+      <c r="J186" s="1"/>
+      <c r="K186" s="1"/>
+      <c r="L186" s="1"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1"/>
+      <c r="B187" s="34"/>
+      <c r="C187" s="52"/>
+      <c r="D187" s="53"/>
+      <c r="E187" s="34"/>
+      <c r="F187" s="34"/>
+      <c r="G187" s="1"/>
+      <c r="H187" s="1"/>
+      <c r="I187" s="1"/>
+      <c r="J187" s="1"/>
+      <c r="K187" s="1"/>
+      <c r="L187" s="1"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1"/>
+      <c r="B188" s="34"/>
+      <c r="C188" s="52"/>
+      <c r="D188" s="53"/>
+      <c r="E188" s="34"/>
+      <c r="F188" s="34"/>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+      <c r="L188" s="1"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1"/>
+      <c r="B189" s="34"/>
+      <c r="C189" s="52"/>
+      <c r="D189" s="53"/>
+      <c r="E189" s="34"/>
+      <c r="F189" s="34"/>
+      <c r="G189" s="1"/>
+      <c r="H189" s="1"/>
+      <c r="I189" s="1"/>
+      <c r="J189" s="1"/>
+      <c r="K189" s="1"/>
+      <c r="L189" s="1"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1"/>
+      <c r="B190" s="34"/>
+      <c r="C190" s="52"/>
+      <c r="D190" s="53"/>
+      <c r="E190" s="34"/>
+      <c r="F190" s="34"/>
+      <c r="G190" s="1"/>
+      <c r="H190" s="1"/>
+      <c r="I190" s="1"/>
+      <c r="J190" s="1"/>
+      <c r="K190" s="1"/>
+      <c r="L190" s="1"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1"/>
+      <c r="B191" s="34"/>
+      <c r="C191" s="52"/>
+      <c r="D191" s="53"/>
+      <c r="E191" s="34"/>
+      <c r="F191" s="34"/>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
+      <c r="K191" s="1"/>
+      <c r="L191" s="1"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1"/>
+      <c r="B192" s="34"/>
+      <c r="C192" s="52"/>
+      <c r="D192" s="53"/>
+      <c r="E192" s="34"/>
+      <c r="F192" s="34"/>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+      <c r="J192" s="1"/>
+      <c r="K192" s="1"/>
+      <c r="L192" s="1"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1"/>
+      <c r="B193" s="34"/>
+      <c r="C193" s="52"/>
+      <c r="D193" s="53"/>
+      <c r="E193" s="34"/>
+      <c r="F193" s="34"/>
+      <c r="G193" s="1"/>
+      <c r="H193" s="1"/>
+      <c r="I193" s="1"/>
+      <c r="J193" s="1"/>
+      <c r="K193" s="1"/>
+      <c r="L193" s="1"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1"/>
+      <c r="B194" s="34"/>
+      <c r="C194" s="52"/>
+      <c r="D194" s="53"/>
+      <c r="E194" s="34"/>
+      <c r="F194" s="34"/>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+      <c r="J194" s="1"/>
+      <c r="K194" s="1"/>
+      <c r="L194" s="1"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1"/>
+      <c r="B195" s="34"/>
+      <c r="C195" s="52"/>
+      <c r="D195" s="53"/>
+      <c r="E195" s="34"/>
+      <c r="F195" s="34"/>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+      <c r="J195" s="1"/>
+      <c r="K195" s="1"/>
+      <c r="L195" s="1"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1"/>
+      <c r="B196" s="34"/>
+      <c r="C196" s="52"/>
+      <c r="D196" s="53"/>
+      <c r="E196" s="34"/>
+      <c r="F196" s="34"/>
+      <c r="G196" s="1"/>
+      <c r="H196" s="1"/>
+      <c r="I196" s="1"/>
+      <c r="J196" s="1"/>
+      <c r="K196" s="1"/>
+      <c r="L196" s="1"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="1"/>
+      <c r="B197" s="34"/>
+      <c r="C197" s="52"/>
+      <c r="D197" s="53"/>
+      <c r="E197" s="34"/>
+      <c r="F197" s="34"/>
+      <c r="G197" s="1"/>
+      <c r="H197" s="1"/>
+      <c r="I197" s="1"/>
+      <c r="J197" s="1"/>
+      <c r="K197" s="1"/>
+      <c r="L197" s="1"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1"/>
+      <c r="B198" s="34"/>
+      <c r="C198" s="52"/>
+      <c r="D198" s="53"/>
+      <c r="E198" s="34"/>
+      <c r="F198" s="34"/>
+      <c r="G198" s="1"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="1"/>
+      <c r="J198" s="1"/>
+      <c r="K198" s="1"/>
+      <c r="L198" s="1"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="1"/>
+      <c r="B199" s="34"/>
+      <c r="C199" s="52"/>
+      <c r="D199" s="53"/>
+      <c r="E199" s="34"/>
+      <c r="F199" s="34"/>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+      <c r="J199" s="1"/>
+      <c r="K199" s="1"/>
+      <c r="L199" s="1"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1"/>
+      <c r="B200" s="34"/>
+      <c r="C200" s="52"/>
+      <c r="D200" s="53"/>
+      <c r="E200" s="34"/>
+      <c r="F200" s="34"/>
+      <c r="G200" s="1"/>
+      <c r="H200" s="1"/>
+      <c r="I200" s="1"/>
+      <c r="J200" s="1"/>
+      <c r="K200" s="1"/>
+      <c r="L200" s="1"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="1"/>
+      <c r="B201" s="34"/>
+      <c r="C201" s="52"/>
+      <c r="D201" s="53"/>
+      <c r="E201" s="34"/>
+      <c r="F201" s="34"/>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201" s="1"/>
+      <c r="J201" s="1"/>
+      <c r="K201" s="1"/>
+      <c r="L201" s="1"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1"/>
+      <c r="B202" s="34"/>
+      <c r="C202" s="52"/>
+      <c r="D202" s="53"/>
+      <c r="E202" s="34"/>
+      <c r="F202" s="34"/>
+      <c r="G202" s="1"/>
+      <c r="H202" s="1"/>
+      <c r="I202" s="1"/>
+      <c r="J202" s="1"/>
+      <c r="K202" s="1"/>
+      <c r="L202" s="1"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1"/>
+      <c r="B203" s="34"/>
+      <c r="C203" s="52"/>
+      <c r="D203" s="53"/>
+      <c r="E203" s="34"/>
+      <c r="F203" s="34"/>
+      <c r="G203" s="1"/>
+      <c r="H203" s="1"/>
+      <c r="I203" s="1"/>
+      <c r="J203" s="1"/>
+      <c r="K203" s="1"/>
+      <c r="L203" s="1"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="1"/>
+      <c r="B204" s="34"/>
+      <c r="C204" s="52"/>
+      <c r="D204" s="53"/>
+      <c r="E204" s="34"/>
+      <c r="F204" s="34"/>
+      <c r="G204" s="1"/>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1"/>
+      <c r="J204" s="1"/>
+      <c r="K204" s="1"/>
+      <c r="L204" s="1"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1"/>
+      <c r="B205" s="34"/>
+      <c r="C205" s="52"/>
+      <c r="D205" s="53"/>
+      <c r="E205" s="34"/>
+      <c r="F205" s="34"/>
+      <c r="G205" s="1"/>
+      <c r="H205" s="1"/>
+      <c r="I205" s="1"/>
+      <c r="J205" s="1"/>
+      <c r="K205" s="1"/>
+      <c r="L205" s="1"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1"/>
+      <c r="B206" s="34"/>
+      <c r="C206" s="52"/>
+      <c r="D206" s="53"/>
+      <c r="E206" s="34"/>
+      <c r="F206" s="34"/>
+      <c r="G206" s="1"/>
+      <c r="H206" s="1"/>
+      <c r="I206" s="1"/>
+      <c r="J206" s="1"/>
+      <c r="K206" s="1"/>
+      <c r="L206" s="1"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1"/>
+      <c r="B207" s="34"/>
+      <c r="C207" s="52"/>
+      <c r="D207" s="53"/>
+      <c r="E207" s="34"/>
+      <c r="F207" s="34"/>
+      <c r="G207" s="1"/>
+      <c r="H207" s="1"/>
+      <c r="I207" s="1"/>
+      <c r="J207" s="1"/>
+      <c r="K207" s="1"/>
+      <c r="L207" s="1"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1"/>
+      <c r="B208" s="34"/>
+      <c r="C208" s="52"/>
+      <c r="D208" s="53"/>
+      <c r="E208" s="34"/>
+      <c r="F208" s="34"/>
+      <c r="G208" s="1"/>
+      <c r="H208" s="1"/>
+      <c r="I208" s="1"/>
+      <c r="J208" s="1"/>
+      <c r="K208" s="1"/>
+      <c r="L208" s="1"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1"/>
+      <c r="B209" s="34"/>
+      <c r="C209" s="52"/>
+      <c r="D209" s="53"/>
+      <c r="E209" s="34"/>
+      <c r="F209" s="34"/>
+      <c r="G209" s="1"/>
+      <c r="H209" s="1"/>
+      <c r="I209" s="1"/>
+      <c r="J209" s="1"/>
+      <c r="K209" s="1"/>
+      <c r="L209" s="1"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1"/>
+      <c r="B210" s="34"/>
+      <c r="C210" s="52"/>
+      <c r="D210" s="53"/>
+      <c r="E210" s="34"/>
+      <c r="F210" s="34"/>
+      <c r="G210" s="1"/>
+      <c r="H210" s="1"/>
+      <c r="I210" s="1"/>
+      <c r="J210" s="1"/>
+      <c r="K210" s="1"/>
+      <c r="L210" s="1"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1"/>
+      <c r="B211" s="34"/>
+      <c r="C211" s="52"/>
+      <c r="D211" s="53"/>
+      <c r="E211" s="34"/>
+      <c r="F211" s="34"/>
+      <c r="G211" s="1"/>
+      <c r="H211" s="1"/>
+      <c r="I211" s="1"/>
+      <c r="J211" s="1"/>
+      <c r="K211" s="1"/>
+      <c r="L211" s="1"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="1"/>
+      <c r="B212" s="34"/>
+      <c r="C212" s="52"/>
+      <c r="D212" s="53"/>
+      <c r="E212" s="34"/>
+      <c r="F212" s="34"/>
+      <c r="G212" s="1"/>
+      <c r="H212" s="1"/>
+      <c r="I212" s="1"/>
+      <c r="J212" s="1"/>
+      <c r="K212" s="1"/>
+      <c r="L212" s="1"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="1"/>
+      <c r="B213" s="34"/>
+      <c r="C213" s="52"/>
+      <c r="D213" s="53"/>
+      <c r="E213" s="34"/>
+      <c r="F213" s="34"/>
+      <c r="G213" s="1"/>
+      <c r="H213" s="1"/>
+      <c r="I213" s="1"/>
+      <c r="J213" s="1"/>
+      <c r="K213" s="1"/>
+      <c r="L213" s="1"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="1"/>
+      <c r="B214" s="34"/>
+      <c r="C214" s="52"/>
+      <c r="D214" s="53"/>
+      <c r="E214" s="34"/>
+      <c r="F214" s="34"/>
+      <c r="G214" s="1"/>
+      <c r="H214" s="1"/>
+      <c r="I214" s="1"/>
+      <c r="J214" s="1"/>
+      <c r="K214" s="1"/>
+      <c r="L214" s="1"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="1"/>
+      <c r="B215" s="34"/>
+      <c r="C215" s="52"/>
+      <c r="D215" s="53"/>
+      <c r="E215" s="34"/>
+      <c r="F215" s="34"/>
+      <c r="G215" s="1"/>
+      <c r="H215" s="1"/>
+      <c r="I215" s="1"/>
+      <c r="J215" s="1"/>
+      <c r="K215" s="1"/>
+      <c r="L215" s="1"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="1"/>
+      <c r="B216" s="34"/>
+      <c r="C216" s="52"/>
+      <c r="D216" s="53"/>
+      <c r="E216" s="34"/>
+      <c r="F216" s="34"/>
+      <c r="G216" s="1"/>
+      <c r="H216" s="1"/>
+      <c r="I216" s="1"/>
+      <c r="J216" s="1"/>
+      <c r="K216" s="1"/>
+      <c r="L216" s="1"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="1"/>
+      <c r="B217" s="34"/>
+      <c r="C217" s="52"/>
+      <c r="D217" s="53"/>
+      <c r="E217" s="34"/>
+      <c r="F217" s="34"/>
+      <c r="G217" s="1"/>
+      <c r="H217" s="1"/>
+      <c r="I217" s="1"/>
+      <c r="J217" s="1"/>
+      <c r="K217" s="1"/>
+      <c r="L217" s="1"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="1"/>
+      <c r="B218" s="34"/>
+      <c r="C218" s="52"/>
+      <c r="D218" s="53"/>
+      <c r="E218" s="34"/>
+      <c r="F218" s="34"/>
+      <c r="G218" s="1"/>
+      <c r="H218" s="1"/>
+      <c r="I218" s="1"/>
+      <c r="J218" s="1"/>
+      <c r="K218" s="1"/>
+      <c r="L218" s="1"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="1"/>
+      <c r="B219" s="34"/>
+      <c r="C219" s="52"/>
+      <c r="D219" s="53"/>
+      <c r="E219" s="34"/>
+      <c r="F219" s="34"/>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+      <c r="J219" s="1"/>
+      <c r="K219" s="1"/>
+      <c r="L219" s="1"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="1"/>
+      <c r="B220" s="34"/>
+      <c r="C220" s="52"/>
+      <c r="D220" s="53"/>
+      <c r="E220" s="34"/>
+      <c r="F220" s="34"/>
+      <c r="G220" s="1"/>
+      <c r="H220" s="1"/>
+      <c r="I220" s="1"/>
+      <c r="J220" s="1"/>
+      <c r="K220" s="1"/>
+      <c r="L220" s="1"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="1"/>
+      <c r="B221" s="34"/>
+      <c r="C221" s="52"/>
+      <c r="D221" s="53"/>
+      <c r="E221" s="34"/>
+      <c r="F221" s="34"/>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
+      <c r="J221" s="1"/>
+      <c r="K221" s="1"/>
+      <c r="L221" s="1"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="1"/>
+      <c r="B222" s="34"/>
+      <c r="C222" s="52"/>
+      <c r="D222" s="53"/>
+      <c r="E222" s="34"/>
+      <c r="F222" s="34"/>
+      <c r="G222" s="1"/>
+      <c r="H222" s="1"/>
+      <c r="I222" s="1"/>
+      <c r="J222" s="1"/>
+      <c r="K222" s="1"/>
+      <c r="L222" s="1"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="1"/>
+      <c r="B223" s="34"/>
+      <c r="C223" s="52"/>
+      <c r="D223" s="53"/>
+      <c r="E223" s="34"/>
+      <c r="F223" s="34"/>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1"/>
+      <c r="I223" s="1"/>
+      <c r="J223" s="1"/>
+      <c r="K223" s="1"/>
+      <c r="L223" s="1"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1"/>
+      <c r="B224" s="34"/>
+      <c r="C224" s="52"/>
+      <c r="D224" s="53"/>
+      <c r="E224" s="34"/>
+      <c r="F224" s="34"/>
+      <c r="G224" s="1"/>
+      <c r="H224" s="1"/>
+      <c r="I224" s="1"/>
+      <c r="J224" s="1"/>
+      <c r="K224" s="1"/>
+      <c r="L224" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B79:G79"/>
-    <mergeCell ref="B88:G88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="B108:H108"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B9:E9"/>
@@ -4268,6 +5601,14 @@
     <mergeCell ref="H10:L10"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="H24:L24"/>
+    <mergeCell ref="B100:H100"/>
+    <mergeCell ref="B129:G129"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B80:G80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="E93:F93"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Results/Results.xlsx
+++ b/Results/Results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="231">
   <si>
     <t>Protocol Assessment: Compliant vs Rack&amp;Pinion</t>
   </si>
@@ -349,6 +349,12 @@
     <t>Gripper 2 with metal screw</t>
   </si>
   <si>
+    <t xml:space="preserve">New design with metal screw </t>
+  </si>
+  <si>
+    <t>New design with metal screw</t>
+  </si>
+  <si>
     <t>TEST +: TASK-LEVEL GRASPING BENCHMARK</t>
   </si>
   <si>
@@ -380,6 +386,324 @@
   </si>
   <si>
     <t>Standard cube</t>
+  </si>
+  <si>
+    <t>TEST  E-TEXTILES</t>
+  </si>
+  <si>
+    <t>TEST A Characterization</t>
+  </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>Distance Step 0 (cm)</t>
+  </si>
+  <si>
+    <t>Distance Last Step (cm)</t>
+  </si>
+  <si>
+    <t>TEST B</t>
+  </si>
+  <si>
+    <t>Dwell Time 5s</t>
+  </si>
+  <si>
+    <t>Sample \ Distance</t>
+  </si>
+  <si>
+    <t>Step 0 (cm)</t>
+  </si>
+  <si>
+    <t>Initial 1.5 N (cm)</t>
+  </si>
+  <si>
+    <t>Cycle 1:  4.5 N / 1.5 N (cm)</t>
+  </si>
+  <si>
+    <t>Cycle 5:  4.5 N / 1.5 N (cm)</t>
+  </si>
+  <si>
+    <t>Cycle 10:  4.5 N / 1.5 N (cm)</t>
+  </si>
+  <si>
+    <t>Cycle 15:  4.5 N / 1.5 N (cm)</t>
+  </si>
+  <si>
+    <t>Cycle 20:  4.5 N / 1.5 N (cm)</t>
+  </si>
+  <si>
+    <t>5,5/5,374</t>
+  </si>
+  <si>
+    <t>5,46/5,32</t>
+  </si>
+  <si>
+    <t>5,5/5,33</t>
+  </si>
+  <si>
+    <t>5,52/5,39</t>
+  </si>
+  <si>
+    <t>5,51/5,33</t>
+  </si>
+  <si>
+    <t>5,56/5,39</t>
+  </si>
+  <si>
+    <t>5,57/5,44</t>
+  </si>
+  <si>
+    <t>5,59/5,44</t>
+  </si>
+  <si>
+    <t>5,6/5,47</t>
+  </si>
+  <si>
+    <t>5,64/5,48</t>
+  </si>
+  <si>
+    <t>5,48/5,324</t>
+  </si>
+  <si>
+    <t>5,5/5,38</t>
+  </si>
+  <si>
+    <t>5,54/5,354</t>
+  </si>
+  <si>
+    <t>5,55/5,4</t>
+  </si>
+  <si>
+    <t>5,6/5,42</t>
+  </si>
+  <si>
+    <t>5,43/5,342</t>
+  </si>
+  <si>
+    <t>5,472/5,354</t>
+  </si>
+  <si>
+    <t>5,51/5,378</t>
+  </si>
+  <si>
+    <t>5,52/5,342</t>
+  </si>
+  <si>
+    <t>5,5/5,4</t>
+  </si>
+  <si>
+    <t>5,56/5,42</t>
+  </si>
+  <si>
+    <t>5,58/5,45</t>
+  </si>
+  <si>
+    <t>5,58/5,464</t>
+  </si>
+  <si>
+    <t>5,59/5,478</t>
+  </si>
+  <si>
+    <t>5,55/5,38</t>
+  </si>
+  <si>
+    <t>5,57/5,4</t>
+  </si>
+  <si>
+    <t>5,57/5,41</t>
+  </si>
+  <si>
+    <t>5,58/5,42</t>
+  </si>
+  <si>
+    <t>5,66/5,5</t>
+  </si>
+  <si>
+    <t>5,65/5,55</t>
+  </si>
+  <si>
+    <t>5,68/5,53</t>
+  </si>
+  <si>
+    <t>5,69/5,57</t>
+  </si>
+  <si>
+    <t>5,696/5,58</t>
+  </si>
+  <si>
+    <t>Dwell Time 10s</t>
+  </si>
+  <si>
+    <t>5,55/5,43</t>
+  </si>
+  <si>
+    <t>5,6/5,48</t>
+  </si>
+  <si>
+    <t>5,62/5,5</t>
+  </si>
+  <si>
+    <t>5,63/5,52</t>
+  </si>
+  <si>
+    <t>5,636/5,52</t>
+  </si>
+  <si>
+    <t>5,55/5,36</t>
+  </si>
+  <si>
+    <t>5,57/5,43</t>
+  </si>
+  <si>
+    <t>5,6/5,46</t>
+  </si>
+  <si>
+    <t>5,422/5,26</t>
+  </si>
+  <si>
+    <t>5,47/5,3</t>
+  </si>
+  <si>
+    <t>5,48/5,34</t>
+  </si>
+  <si>
+    <t>5,482/5,32</t>
+  </si>
+  <si>
+    <t>5,5/5,34</t>
+  </si>
+  <si>
+    <t>5,39/5,26</t>
+  </si>
+  <si>
+    <t>5,42/5,28</t>
+  </si>
+  <si>
+    <t>5,47/5,32</t>
+  </si>
+  <si>
+    <t>5,45/5,324</t>
+  </si>
+  <si>
+    <t>5,48/5,33</t>
+  </si>
+  <si>
+    <t>5,5/5,35</t>
+  </si>
+  <si>
+    <t>5,52/5,452</t>
+  </si>
+  <si>
+    <t>5,56/5,45</t>
+  </si>
+  <si>
+    <t>5,552/5,448</t>
+  </si>
+  <si>
+    <t>5,57/5,452</t>
+  </si>
+  <si>
+    <t>5,48/5,392</t>
+  </si>
+  <si>
+    <t>5,56/5,43</t>
+  </si>
+  <si>
+    <t>5,57/5,45</t>
+  </si>
+  <si>
+    <t>5,51/5,364</t>
+  </si>
+  <si>
+    <t>5,516/5,354</t>
+  </si>
+  <si>
+    <t>5,542/5,4</t>
+  </si>
+  <si>
+    <t>Dwell Time 30s</t>
+  </si>
+  <si>
+    <t>5,52/5,4</t>
+  </si>
+  <si>
+    <t>5,564/5,43</t>
+  </si>
+  <si>
+    <t>5,582/5,47</t>
+  </si>
+  <si>
+    <t>5,59/5,476</t>
+  </si>
+  <si>
+    <t>5,47/5,39</t>
+  </si>
+  <si>
+    <t>5,526/5,4</t>
+  </si>
+  <si>
+    <t>5,626/5,5</t>
+  </si>
+  <si>
+    <t>5,63/5,53</t>
+  </si>
+  <si>
+    <t>5,66/5,534</t>
+  </si>
+  <si>
+    <t>5,68/5,534</t>
+  </si>
+  <si>
+    <t>5,55/5,384</t>
+  </si>
+  <si>
+    <t>5,576/5,42</t>
+  </si>
+  <si>
+    <t>5,58/5,426</t>
+  </si>
+  <si>
+    <t>5,59/5,43</t>
+  </si>
+  <si>
+    <t>5,49/5,37</t>
+  </si>
+  <si>
+    <t>5,53/5,392</t>
+  </si>
+  <si>
+    <t>5,534/5,41</t>
+  </si>
+  <si>
+    <t>5,54/5,416</t>
+  </si>
+  <si>
+    <t>5,55/5,418</t>
+  </si>
+  <si>
+    <t>5,55/5,39</t>
+  </si>
+  <si>
+    <t>5,572/5,44</t>
+  </si>
+  <si>
+    <t>5,578/5,448</t>
+  </si>
+  <si>
+    <t>5,536/5,342</t>
+  </si>
+  <si>
+    <t>5,542/5,368</t>
+  </si>
+  <si>
+    <t>5,56/5,37</t>
+  </si>
+  <si>
+    <t>5,566/5,4</t>
+  </si>
+  <si>
+    <t>5,564/5,4</t>
   </si>
 </sst>
 </file>
@@ -424,7 +748,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -467,8 +791,14 @@
         <bgColor rgb="FFEA9999"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC27BA0"/>
+        <bgColor rgb="FFC27BA0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border/>
     <border>
       <left style="thin">
@@ -601,11 +931,19 @@
         <color rgb="FF74777E"/>
       </top>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF74777E"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF74777E"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="72">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -630,19 +968,19 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -689,13 +1027,13 @@
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="10" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -720,40 +1058,40 @@
     <xf borderId="13" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="6" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="7" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -762,7 +1100,19 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -774,13 +1124,13 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -794,6 +1144,15 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="11" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4189,13 +4548,29 @@
     </row>
     <row r="126">
       <c r="A126" s="1"/>
-      <c r="B126" s="34"/>
-      <c r="C126" s="52"/>
-      <c r="D126" s="53"/>
-      <c r="E126" s="34"/>
-      <c r="F126" s="34"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
+      <c r="B126" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="C126" s="55">
+        <v>1.0</v>
+      </c>
+      <c r="D126" s="56">
+        <v>39.7</v>
+      </c>
+      <c r="E126" s="54">
+        <v>0.474</v>
+      </c>
+      <c r="F126" s="54">
+        <v>5.155</v>
+      </c>
+      <c r="G126" s="57">
+        <f t="shared" ref="G126:G130" si="13">E126*F126</f>
+        <v>2.44347</v>
+      </c>
+      <c r="H126" s="57">
+        <f t="shared" ref="H126:H130" si="14">IFERROR(D126/G126, 0)</f>
+        <v>16.24738589</v>
+      </c>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
@@ -4203,13 +4578,29 @@
     </row>
     <row r="127">
       <c r="A127" s="1"/>
-      <c r="B127" s="34"/>
-      <c r="C127" s="52"/>
-      <c r="D127" s="53"/>
-      <c r="E127" s="34"/>
-      <c r="F127" s="34"/>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
+      <c r="B127" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C127" s="55">
+        <v>2.0</v>
+      </c>
+      <c r="D127" s="56">
+        <v>29.82</v>
+      </c>
+      <c r="E127" s="54">
+        <v>0.478</v>
+      </c>
+      <c r="F127" s="54">
+        <v>5.147</v>
+      </c>
+      <c r="G127" s="57">
+        <f t="shared" si="13"/>
+        <v>2.460266</v>
+      </c>
+      <c r="H127" s="57">
+        <f t="shared" si="14"/>
+        <v>12.12064061</v>
+      </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
@@ -4217,13 +4608,29 @@
     </row>
     <row r="128">
       <c r="A128" s="1"/>
-      <c r="B128" s="34"/>
-      <c r="C128" s="52"/>
-      <c r="D128" s="53"/>
-      <c r="E128" s="34"/>
-      <c r="F128" s="34"/>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
+      <c r="B128" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C128" s="55">
+        <v>3.0</v>
+      </c>
+      <c r="D128" s="56">
+        <v>29.84</v>
+      </c>
+      <c r="E128" s="54">
+        <v>0.462</v>
+      </c>
+      <c r="F128" s="54">
+        <v>5.155</v>
+      </c>
+      <c r="G128" s="57">
+        <f t="shared" si="13"/>
+        <v>2.38161</v>
+      </c>
+      <c r="H128" s="57">
+        <f t="shared" si="14"/>
+        <v>12.5293394</v>
+      </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
@@ -4232,9 +4639,28 @@
     <row r="129">
       <c r="A129" s="1"/>
       <c r="B129" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="H129" s="1"/>
+        <v>113</v>
+      </c>
+      <c r="C129" s="55">
+        <v>4.0</v>
+      </c>
+      <c r="D129" s="56">
+        <v>36.11</v>
+      </c>
+      <c r="E129" s="54">
+        <v>0.458</v>
+      </c>
+      <c r="F129" s="54">
+        <v>5.147</v>
+      </c>
+      <c r="G129" s="57">
+        <f t="shared" si="13"/>
+        <v>2.357326</v>
+      </c>
+      <c r="H129" s="57">
+        <f t="shared" si="14"/>
+        <v>15.31820376</v>
+      </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
@@ -4242,13 +4668,29 @@
     </row>
     <row r="130">
       <c r="A130" s="1"/>
-      <c r="B130" s="55"/>
-      <c r="C130" s="56"/>
-      <c r="D130" s="57"/>
-      <c r="E130" s="55"/>
-      <c r="F130" s="55"/>
-      <c r="G130" s="56"/>
-      <c r="H130" s="1"/>
+      <c r="B130" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C130" s="55">
+        <v>5.0</v>
+      </c>
+      <c r="D130" s="56">
+        <v>41.1</v>
+      </c>
+      <c r="E130" s="54">
+        <v>0.462</v>
+      </c>
+      <c r="F130" s="54">
+        <v>5.163</v>
+      </c>
+      <c r="G130" s="57">
+        <f t="shared" si="13"/>
+        <v>2.385306</v>
+      </c>
+      <c r="H130" s="57">
+        <f t="shared" si="14"/>
+        <v>17.2304937</v>
+      </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
@@ -4256,24 +4698,12 @@
     </row>
     <row r="131">
       <c r="A131" s="1"/>
-      <c r="B131" s="58" t="s">
-        <v>113</v>
-      </c>
-      <c r="C131" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="D131" s="60" t="s">
-        <v>115</v>
-      </c>
-      <c r="E131" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F131" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="G131" s="59" t="s">
-        <v>68</v>
-      </c>
+      <c r="B131" s="34"/>
+      <c r="C131" s="52"/>
+      <c r="D131" s="53"/>
+      <c r="E131" s="34"/>
+      <c r="F131" s="34"/>
+      <c r="G131" s="1"/>
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -4282,14 +4712,9 @@
     </row>
     <row r="132">
       <c r="A132" s="1"/>
-      <c r="B132" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="C132" s="62"/>
-      <c r="D132" s="63"/>
-      <c r="E132" s="64"/>
-      <c r="F132" s="64"/>
-      <c r="G132" s="62"/>
+      <c r="B132" s="58" t="s">
+        <v>114</v>
+      </c>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -4298,14 +4723,12 @@
     </row>
     <row r="133">
       <c r="A133" s="1"/>
-      <c r="B133" s="61" t="s">
-        <v>119</v>
-      </c>
-      <c r="C133" s="62"/>
-      <c r="D133" s="63"/>
-      <c r="E133" s="64"/>
-      <c r="F133" s="64"/>
-      <c r="G133" s="62"/>
+      <c r="B133" s="59"/>
+      <c r="C133" s="60"/>
+      <c r="D133" s="61"/>
+      <c r="E133" s="59"/>
+      <c r="F133" s="59"/>
+      <c r="G133" s="60"/>
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -4314,14 +4737,24 @@
     </row>
     <row r="134">
       <c r="A134" s="1"/>
-      <c r="B134" s="61" t="s">
-        <v>120</v>
-      </c>
-      <c r="C134" s="62"/>
-      <c r="D134" s="63"/>
-      <c r="E134" s="64"/>
-      <c r="F134" s="64"/>
-      <c r="G134" s="62"/>
+      <c r="B134" s="62" t="s">
+        <v>115</v>
+      </c>
+      <c r="C134" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="D134" s="64" t="s">
+        <v>117</v>
+      </c>
+      <c r="E134" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="F134" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="G134" s="63" t="s">
+        <v>68</v>
+      </c>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -4330,14 +4763,14 @@
     </row>
     <row r="135">
       <c r="A135" s="1"/>
-      <c r="B135" s="61" t="s">
-        <v>121</v>
-      </c>
-      <c r="C135" s="62"/>
-      <c r="D135" s="63"/>
-      <c r="E135" s="64"/>
-      <c r="F135" s="64"/>
-      <c r="G135" s="62"/>
+      <c r="B135" s="65" t="s">
+        <v>120</v>
+      </c>
+      <c r="C135" s="66"/>
+      <c r="D135" s="67"/>
+      <c r="E135" s="68"/>
+      <c r="F135" s="68"/>
+      <c r="G135" s="66"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -4346,14 +4779,14 @@
     </row>
     <row r="136">
       <c r="A136" s="1"/>
-      <c r="B136" s="61" t="s">
-        <v>122</v>
-      </c>
-      <c r="C136" s="62"/>
-      <c r="D136" s="63"/>
-      <c r="E136" s="64"/>
-      <c r="F136" s="64"/>
-      <c r="G136" s="62"/>
+      <c r="B136" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="C136" s="66"/>
+      <c r="D136" s="67"/>
+      <c r="E136" s="68"/>
+      <c r="F136" s="68"/>
+      <c r="G136" s="66"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -4362,12 +4795,14 @@
     </row>
     <row r="137">
       <c r="A137" s="1"/>
-      <c r="B137" s="34"/>
-      <c r="C137" s="52"/>
-      <c r="D137" s="53"/>
-      <c r="E137" s="34"/>
-      <c r="F137" s="34"/>
-      <c r="G137" s="1"/>
+      <c r="B137" s="65" t="s">
+        <v>122</v>
+      </c>
+      <c r="C137" s="66"/>
+      <c r="D137" s="67"/>
+      <c r="E137" s="68"/>
+      <c r="F137" s="68"/>
+      <c r="G137" s="66"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -4376,12 +4811,14 @@
     </row>
     <row r="138">
       <c r="A138" s="1"/>
-      <c r="B138" s="34"/>
-      <c r="C138" s="52"/>
-      <c r="D138" s="53"/>
-      <c r="E138" s="34"/>
-      <c r="F138" s="34"/>
-      <c r="G138" s="1"/>
+      <c r="B138" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="C138" s="66"/>
+      <c r="D138" s="67"/>
+      <c r="E138" s="68"/>
+      <c r="F138" s="68"/>
+      <c r="G138" s="66"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -4390,12 +4827,14 @@
     </row>
     <row r="139">
       <c r="A139" s="1"/>
-      <c r="B139" s="34"/>
-      <c r="C139" s="52"/>
-      <c r="D139" s="53"/>
-      <c r="E139" s="34"/>
-      <c r="F139" s="34"/>
-      <c r="G139" s="1"/>
+      <c r="B139" s="65" t="s">
+        <v>124</v>
+      </c>
+      <c r="C139" s="66"/>
+      <c r="D139" s="67"/>
+      <c r="E139" s="68"/>
+      <c r="F139" s="68"/>
+      <c r="G139" s="66"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -4432,12 +4871,9 @@
     </row>
     <row r="142">
       <c r="A142" s="1"/>
-      <c r="B142" s="34"/>
-      <c r="C142" s="52"/>
-      <c r="D142" s="53"/>
-      <c r="E142" s="34"/>
-      <c r="F142" s="34"/>
-      <c r="G142" s="1"/>
+      <c r="B142" s="58" t="s">
+        <v>125</v>
+      </c>
       <c r="H142" s="1"/>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -4446,12 +4882,9 @@
     </row>
     <row r="143">
       <c r="A143" s="1"/>
-      <c r="B143" s="34"/>
-      <c r="C143" s="52"/>
-      <c r="D143" s="53"/>
-      <c r="E143" s="34"/>
-      <c r="F143" s="34"/>
-      <c r="G143" s="1"/>
+      <c r="B143" s="7" t="s">
+        <v>126</v>
+      </c>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -4461,9 +4894,15 @@
     <row r="144">
       <c r="A144" s="1"/>
       <c r="B144" s="34"/>
-      <c r="C144" s="52"/>
-      <c r="D144" s="53"/>
-      <c r="E144" s="34"/>
+      <c r="C144" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>129</v>
+      </c>
       <c r="F144" s="34"/>
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
@@ -4475,9 +4914,15 @@
     <row r="145">
       <c r="A145" s="1"/>
       <c r="B145" s="34"/>
-      <c r="C145" s="52"/>
-      <c r="D145" s="53"/>
-      <c r="E145" s="34"/>
+      <c r="C145" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="D145" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E145" s="6">
+        <v>5.39</v>
+      </c>
       <c r="F145" s="34"/>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -4489,9 +4934,15 @@
     <row r="146">
       <c r="A146" s="1"/>
       <c r="B146" s="34"/>
-      <c r="C146" s="52"/>
-      <c r="D146" s="53"/>
-      <c r="E146" s="34"/>
+      <c r="C146" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="D146" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E146" s="6">
+        <v>5.31</v>
+      </c>
       <c r="F146" s="34"/>
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
@@ -4503,9 +4954,15 @@
     <row r="147">
       <c r="A147" s="1"/>
       <c r="B147" s="34"/>
-      <c r="C147" s="52"/>
-      <c r="D147" s="53"/>
-      <c r="E147" s="34"/>
+      <c r="C147" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="D147" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E147" s="6">
+        <v>5.29</v>
+      </c>
       <c r="F147" s="34"/>
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
@@ -4517,9 +4974,15 @@
     <row r="148">
       <c r="A148" s="1"/>
       <c r="B148" s="34"/>
-      <c r="C148" s="52"/>
-      <c r="D148" s="53"/>
-      <c r="E148" s="34"/>
+      <c r="C148" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D148" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E148" s="6">
+        <v>5.32</v>
+      </c>
       <c r="F148" s="34"/>
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
@@ -4531,9 +4994,15 @@
     <row r="149">
       <c r="A149" s="1"/>
       <c r="B149" s="34"/>
-      <c r="C149" s="52"/>
-      <c r="D149" s="53"/>
-      <c r="E149" s="34"/>
+      <c r="C149" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D149" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E149" s="6">
+        <v>5.316</v>
+      </c>
       <c r="F149" s="34"/>
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
@@ -4545,9 +5014,15 @@
     <row r="150">
       <c r="A150" s="1"/>
       <c r="B150" s="34"/>
-      <c r="C150" s="52"/>
-      <c r="D150" s="53"/>
-      <c r="E150" s="34"/>
+      <c r="C150" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="D150" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E150" s="6">
+        <v>5.286</v>
+      </c>
       <c r="F150" s="34"/>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
@@ -4559,9 +5034,15 @@
     <row r="151">
       <c r="A151" s="1"/>
       <c r="B151" s="34"/>
-      <c r="C151" s="52"/>
-      <c r="D151" s="53"/>
-      <c r="E151" s="34"/>
+      <c r="C151" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="D151" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E151" s="6">
+        <v>5.31</v>
+      </c>
       <c r="F151" s="34"/>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -4573,9 +5054,15 @@
     <row r="152">
       <c r="A152" s="1"/>
       <c r="B152" s="34"/>
-      <c r="C152" s="52"/>
-      <c r="D152" s="53"/>
-      <c r="E152" s="34"/>
+      <c r="C152" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="D152" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E152" s="6">
+        <v>5.3</v>
+      </c>
       <c r="F152" s="34"/>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -4587,9 +5074,15 @@
     <row r="153">
       <c r="A153" s="1"/>
       <c r="B153" s="34"/>
-      <c r="C153" s="52"/>
-      <c r="D153" s="53"/>
-      <c r="E153" s="34"/>
+      <c r="C153" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="D153" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E153" s="6">
+        <v>5.29</v>
+      </c>
       <c r="F153" s="34"/>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -4601,9 +5094,15 @@
     <row r="154">
       <c r="A154" s="1"/>
       <c r="B154" s="34"/>
-      <c r="C154" s="52"/>
-      <c r="D154" s="53"/>
-      <c r="E154" s="34"/>
+      <c r="C154" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="D154" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E154" s="6">
+        <v>5.286</v>
+      </c>
       <c r="F154" s="34"/>
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
@@ -4615,9 +5114,15 @@
     <row r="155">
       <c r="A155" s="1"/>
       <c r="B155" s="34"/>
-      <c r="C155" s="52"/>
-      <c r="D155" s="53"/>
-      <c r="E155" s="34"/>
+      <c r="C155" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="D155" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E155" s="6">
+        <v>5.282</v>
+      </c>
       <c r="F155" s="34"/>
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
@@ -4629,9 +5134,15 @@
     <row r="156">
       <c r="A156" s="1"/>
       <c r="B156" s="34"/>
-      <c r="C156" s="52"/>
-      <c r="D156" s="53"/>
-      <c r="E156" s="34"/>
+      <c r="C156" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="D156" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E156" s="6">
+        <v>5.28</v>
+      </c>
       <c r="F156" s="34"/>
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
@@ -4643,9 +5154,15 @@
     <row r="157">
       <c r="A157" s="1"/>
       <c r="B157" s="34"/>
-      <c r="C157" s="52"/>
-      <c r="D157" s="53"/>
-      <c r="E157" s="34"/>
+      <c r="C157" s="6">
+        <v>13.0</v>
+      </c>
+      <c r="D157" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E157" s="6">
+        <v>5.262</v>
+      </c>
       <c r="F157" s="34"/>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
@@ -4657,9 +5174,15 @@
     <row r="158">
       <c r="A158" s="1"/>
       <c r="B158" s="34"/>
-      <c r="C158" s="52"/>
-      <c r="D158" s="53"/>
-      <c r="E158" s="34"/>
+      <c r="C158" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="D158" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E158" s="6">
+        <v>5.26</v>
+      </c>
       <c r="F158" s="34"/>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -4684,392 +5207,756 @@
     </row>
     <row r="160">
       <c r="A160" s="1"/>
-      <c r="B160" s="34"/>
-      <c r="C160" s="52"/>
-      <c r="D160" s="53"/>
-      <c r="E160" s="34"/>
-      <c r="F160" s="34"/>
-      <c r="G160" s="1"/>
-      <c r="H160" s="1"/>
-      <c r="I160" s="1"/>
+      <c r="B160" s="69" t="s">
+        <v>130</v>
+      </c>
       <c r="J160" s="1"/>
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
     </row>
     <row r="161">
       <c r="A161" s="1"/>
-      <c r="B161" s="34"/>
-      <c r="C161" s="52"/>
-      <c r="D161" s="53"/>
-      <c r="E161" s="34"/>
-      <c r="F161" s="34"/>
-      <c r="G161" s="1"/>
-      <c r="H161" s="1"/>
-      <c r="I161" s="1"/>
+      <c r="B161" s="69" t="s">
+        <v>131</v>
+      </c>
       <c r="J161" s="1"/>
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
     </row>
     <row r="162">
       <c r="A162" s="1"/>
-      <c r="B162" s="34"/>
-      <c r="C162" s="52"/>
-      <c r="D162" s="53"/>
-      <c r="E162" s="34"/>
-      <c r="F162" s="34"/>
-      <c r="G162" s="1"/>
-      <c r="H162" s="1"/>
-      <c r="I162" s="1"/>
+      <c r="B162" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C162" s="70" t="s">
+        <v>133</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>139</v>
+      </c>
       <c r="J162" s="1"/>
       <c r="K162" s="1"/>
       <c r="L162" s="1"/>
     </row>
     <row r="163">
       <c r="A163" s="1"/>
-      <c r="B163" s="34"/>
-      <c r="C163" s="52"/>
-      <c r="D163" s="53"/>
-      <c r="E163" s="34"/>
-      <c r="F163" s="34"/>
-      <c r="G163" s="1"/>
-      <c r="H163" s="1"/>
-      <c r="I163" s="1"/>
+      <c r="B163" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="C163" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D163" s="14">
+        <v>5.2</v>
+      </c>
+      <c r="E163" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="F163" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="G163" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="H163" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I163" s="14" t="s">
+        <v>144</v>
+      </c>
       <c r="J163" s="1"/>
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
     </row>
     <row r="164">
       <c r="A164" s="1"/>
-      <c r="B164" s="34"/>
-      <c r="C164" s="52"/>
-      <c r="D164" s="53"/>
-      <c r="E164" s="34"/>
-      <c r="F164" s="34"/>
-      <c r="G164" s="1"/>
-      <c r="H164" s="1"/>
-      <c r="I164" s="1"/>
+      <c r="B164" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="C164" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D164" s="14">
+        <v>5.2</v>
+      </c>
+      <c r="E164" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="F164" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G164" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="H164" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="I164" s="14" t="s">
+        <v>149</v>
+      </c>
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
       <c r="L164" s="1"/>
     </row>
     <row r="165">
       <c r="A165" s="1"/>
-      <c r="B165" s="34"/>
-      <c r="C165" s="52"/>
-      <c r="D165" s="53"/>
-      <c r="E165" s="34"/>
-      <c r="F165" s="34"/>
-      <c r="G165" s="1"/>
-      <c r="H165" s="1"/>
-      <c r="I165" s="1"/>
+      <c r="B165" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="C165" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D165" s="14">
+        <v>5.18</v>
+      </c>
+      <c r="E165" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F165" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="G165" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="H165" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="I165" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
     </row>
     <row r="166">
       <c r="A166" s="1"/>
-      <c r="B166" s="34"/>
-      <c r="C166" s="52"/>
-      <c r="D166" s="53"/>
-      <c r="E166" s="34"/>
-      <c r="F166" s="34"/>
-      <c r="G166" s="1"/>
-      <c r="H166" s="1"/>
-      <c r="I166" s="1"/>
+      <c r="B166" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C166" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D166" s="14">
+        <v>5.13</v>
+      </c>
+      <c r="E166" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F166" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="G166" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="H166" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="I166" s="14" t="s">
+        <v>158</v>
+      </c>
       <c r="J166" s="1"/>
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
     </row>
     <row r="167">
       <c r="A167" s="1"/>
-      <c r="B167" s="34"/>
-      <c r="C167" s="52"/>
-      <c r="D167" s="53"/>
-      <c r="E167" s="34"/>
-      <c r="F167" s="34"/>
-      <c r="G167" s="1"/>
-      <c r="H167" s="1"/>
-      <c r="I167" s="1"/>
+      <c r="B167" s="38">
+        <v>5.0</v>
+      </c>
+      <c r="C167" s="71">
+        <v>5.0</v>
+      </c>
+      <c r="D167" s="14">
+        <v>5.18</v>
+      </c>
+      <c r="E167" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="F167" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G167" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H167" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="I167" s="14" t="s">
+        <v>163</v>
+      </c>
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
     </row>
     <row r="168">
       <c r="A168" s="1"/>
-      <c r="B168" s="34"/>
-      <c r="C168" s="52"/>
-      <c r="D168" s="53"/>
-      <c r="E168" s="34"/>
-      <c r="F168" s="34"/>
-      <c r="G168" s="1"/>
-      <c r="H168" s="1"/>
-      <c r="I168" s="1"/>
+      <c r="B168" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="C168" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="D168" s="14">
+        <v>5.17</v>
+      </c>
+      <c r="E168" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F168" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="G168" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="H168" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="I168" s="14" t="s">
+        <v>148</v>
+      </c>
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
     </row>
     <row r="169">
       <c r="A169" s="1"/>
-      <c r="B169" s="34"/>
-      <c r="C169" s="52"/>
-      <c r="D169" s="53"/>
-      <c r="E169" s="34"/>
-      <c r="F169" s="34"/>
-      <c r="G169" s="1"/>
-      <c r="H169" s="1"/>
-      <c r="I169" s="1"/>
+      <c r="B169" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="C169" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="D169" s="14">
+        <v>5.254</v>
+      </c>
+      <c r="E169" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F169" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G169" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H169" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="I169" s="14" t="s">
+        <v>172</v>
+      </c>
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
       <c r="L169" s="1"/>
     </row>
     <row r="170">
       <c r="A170" s="1"/>
-      <c r="B170" s="34"/>
-      <c r="C170" s="52"/>
-      <c r="D170" s="53"/>
-      <c r="E170" s="34"/>
-      <c r="F170" s="34"/>
-      <c r="G170" s="1"/>
-      <c r="H170" s="1"/>
-      <c r="I170" s="1"/>
+      <c r="B170" s="69" t="s">
+        <v>173</v>
+      </c>
       <c r="J170" s="1"/>
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
     </row>
     <row r="171">
       <c r="A171" s="1"/>
-      <c r="B171" s="34"/>
-      <c r="C171" s="52"/>
-      <c r="D171" s="53"/>
-      <c r="E171" s="34"/>
-      <c r="F171" s="34"/>
-      <c r="G171" s="1"/>
-      <c r="H171" s="1"/>
-      <c r="I171" s="1"/>
+      <c r="B171" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C171" s="70" t="s">
+        <v>133</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H171" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I171" s="8" t="s">
+        <v>139</v>
+      </c>
       <c r="J171" s="1"/>
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
     </row>
     <row r="172">
       <c r="A172" s="1"/>
-      <c r="B172" s="34"/>
-      <c r="C172" s="52"/>
-      <c r="D172" s="53"/>
-      <c r="E172" s="34"/>
-      <c r="F172" s="34"/>
-      <c r="G172" s="1"/>
-      <c r="H172" s="1"/>
-      <c r="I172" s="1"/>
+      <c r="B172" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="C172" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D172" s="14">
+        <v>5.23</v>
+      </c>
+      <c r="E172" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F172" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G172" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="H172" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="I172" s="14" t="s">
+        <v>178</v>
+      </c>
       <c r="J172" s="1"/>
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
     </row>
     <row r="173">
       <c r="A173" s="1"/>
-      <c r="B173" s="34"/>
-      <c r="C173" s="52"/>
-      <c r="D173" s="53"/>
-      <c r="E173" s="34"/>
-      <c r="F173" s="34"/>
-      <c r="G173" s="1"/>
-      <c r="H173" s="1"/>
-      <c r="I173" s="1"/>
+      <c r="B173" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="C173" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D173" s="14">
+        <v>5.2</v>
+      </c>
+      <c r="E173" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="F173" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G173" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="H173" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="I173" s="14" t="s">
+        <v>181</v>
+      </c>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
     </row>
     <row r="174">
       <c r="A174" s="1"/>
-      <c r="B174" s="34"/>
-      <c r="C174" s="52"/>
-      <c r="D174" s="53"/>
-      <c r="E174" s="34"/>
-      <c r="F174" s="34"/>
-      <c r="G174" s="1"/>
-      <c r="H174" s="1"/>
-      <c r="I174" s="1"/>
+      <c r="B174" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="C174" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D174" s="14">
+        <v>5.12</v>
+      </c>
+      <c r="E174" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="F174" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="G174" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="H174" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="I174" s="14" t="s">
+        <v>186</v>
+      </c>
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
     </row>
     <row r="175">
       <c r="A175" s="1"/>
-      <c r="B175" s="34"/>
-      <c r="C175" s="52"/>
-      <c r="D175" s="53"/>
-      <c r="E175" s="34"/>
-      <c r="F175" s="34"/>
-      <c r="G175" s="1"/>
-      <c r="H175" s="1"/>
-      <c r="I175" s="1"/>
+      <c r="B175" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C175" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D175" s="14">
+        <v>5.06</v>
+      </c>
+      <c r="E175" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="F175" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="G175" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H175" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I175" s="14" t="s">
+        <v>191</v>
+      </c>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
     </row>
     <row r="176">
       <c r="A176" s="1"/>
-      <c r="B176" s="34"/>
-      <c r="C176" s="52"/>
-      <c r="D176" s="53"/>
-      <c r="E176" s="34"/>
-      <c r="F176" s="34"/>
-      <c r="G176" s="1"/>
-      <c r="H176" s="1"/>
-      <c r="I176" s="1"/>
+      <c r="B176" s="38">
+        <v>5.0</v>
+      </c>
+      <c r="C176" s="71">
+        <v>5.0</v>
+      </c>
+      <c r="D176" s="14">
+        <v>5.16</v>
+      </c>
+      <c r="E176" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="F176" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G176" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H176" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="I176" s="14" t="s">
+        <v>196</v>
+      </c>
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
     </row>
     <row r="177">
       <c r="A177" s="1"/>
-      <c r="B177" s="34"/>
-      <c r="C177" s="52"/>
-      <c r="D177" s="53"/>
-      <c r="E177" s="34"/>
-      <c r="F177" s="34"/>
-      <c r="G177" s="1"/>
-      <c r="H177" s="1"/>
-      <c r="I177" s="1"/>
+      <c r="B177" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="C177" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="D177" s="14">
+        <v>5.17</v>
+      </c>
+      <c r="E177" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F177" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="G177" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="H177" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I177" s="14" t="s">
+        <v>199</v>
+      </c>
       <c r="J177" s="1"/>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
     </row>
     <row r="178">
       <c r="A178" s="1"/>
-      <c r="B178" s="34"/>
-      <c r="C178" s="52"/>
-      <c r="D178" s="53"/>
-      <c r="E178" s="34"/>
-      <c r="F178" s="34"/>
-      <c r="G178" s="1"/>
-      <c r="H178" s="1"/>
-      <c r="I178" s="1"/>
+      <c r="B178" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="C178" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="D178" s="14">
+        <v>5.16</v>
+      </c>
+      <c r="E178" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="F178" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="G178" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="H178" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="I178" s="14" t="s">
+        <v>160</v>
+      </c>
       <c r="J178" s="1"/>
       <c r="K178" s="1"/>
       <c r="L178" s="1"/>
     </row>
     <row r="179">
       <c r="A179" s="1"/>
-      <c r="B179" s="34"/>
-      <c r="C179" s="52"/>
-      <c r="D179" s="53"/>
-      <c r="E179" s="34"/>
-      <c r="F179" s="34"/>
-      <c r="G179" s="1"/>
-      <c r="H179" s="1"/>
-      <c r="I179" s="1"/>
+      <c r="B179" s="69" t="s">
+        <v>203</v>
+      </c>
       <c r="J179" s="1"/>
       <c r="K179" s="1"/>
       <c r="L179" s="1"/>
     </row>
     <row r="180">
       <c r="A180" s="1"/>
-      <c r="B180" s="34"/>
-      <c r="C180" s="52"/>
-      <c r="D180" s="53"/>
-      <c r="E180" s="34"/>
-      <c r="F180" s="34"/>
-      <c r="G180" s="1"/>
-      <c r="H180" s="1"/>
-      <c r="I180" s="1"/>
+      <c r="B180" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C180" s="70" t="s">
+        <v>133</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H180" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I180" s="8" t="s">
+        <v>139</v>
+      </c>
       <c r="J180" s="1"/>
       <c r="K180" s="1"/>
       <c r="L180" s="1"/>
     </row>
     <row r="181">
       <c r="A181" s="1"/>
-      <c r="B181" s="34"/>
-      <c r="C181" s="52"/>
-      <c r="D181" s="53"/>
-      <c r="E181" s="34"/>
-      <c r="F181" s="34"/>
-      <c r="G181" s="1"/>
-      <c r="H181" s="1"/>
-      <c r="I181" s="1"/>
+      <c r="B181" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="C181" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D181" s="14">
+        <v>5.19</v>
+      </c>
+      <c r="E181" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F181" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="G181" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H181" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="I181" s="14" t="s">
+        <v>207</v>
+      </c>
       <c r="J181" s="1"/>
       <c r="K181" s="1"/>
       <c r="L181" s="1"/>
     </row>
     <row r="182">
       <c r="A182" s="1"/>
-      <c r="B182" s="34"/>
-      <c r="C182" s="52"/>
-      <c r="D182" s="53"/>
-      <c r="E182" s="34"/>
-      <c r="F182" s="34"/>
-      <c r="G182" s="1"/>
-      <c r="H182" s="1"/>
-      <c r="I182" s="1"/>
+      <c r="B182" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="C182" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D182" s="14">
+        <v>5.174</v>
+      </c>
+      <c r="E182" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="F182" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="G182" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H182" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I182" s="14" t="s">
+        <v>146</v>
+      </c>
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
       <c r="L182" s="1"/>
     </row>
     <row r="183">
       <c r="A183" s="1"/>
-      <c r="B183" s="34"/>
-      <c r="C183" s="52"/>
-      <c r="D183" s="53"/>
-      <c r="E183" s="34"/>
-      <c r="F183" s="34"/>
-      <c r="G183" s="1"/>
-      <c r="H183" s="1"/>
-      <c r="I183" s="1"/>
+      <c r="B183" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="C183" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D183" s="14">
+        <v>5.26</v>
+      </c>
+      <c r="E183" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="F183" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="G183" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="H183" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="I183" s="14" t="s">
+        <v>213</v>
+      </c>
       <c r="J183" s="1"/>
       <c r="K183" s="1"/>
       <c r="L183" s="1"/>
     </row>
     <row r="184">
       <c r="A184" s="1"/>
-      <c r="B184" s="34"/>
-      <c r="C184" s="52"/>
-      <c r="D184" s="53"/>
-      <c r="E184" s="34"/>
-      <c r="F184" s="34"/>
-      <c r="G184" s="1"/>
-      <c r="H184" s="1"/>
-      <c r="I184" s="1"/>
+      <c r="B184" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C184" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D184" s="14">
+        <v>5.17</v>
+      </c>
+      <c r="E184" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F184" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="G184" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="H184" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="I184" s="14" t="s">
+        <v>217</v>
+      </c>
       <c r="J184" s="1"/>
       <c r="K184" s="1"/>
       <c r="L184" s="1"/>
     </row>
     <row r="185">
       <c r="A185" s="1"/>
-      <c r="B185" s="34"/>
-      <c r="C185" s="52"/>
-      <c r="D185" s="53"/>
-      <c r="E185" s="34"/>
-      <c r="F185" s="34"/>
-      <c r="G185" s="1"/>
-      <c r="H185" s="1"/>
-      <c r="I185" s="1"/>
+      <c r="B185" s="38">
+        <v>5.0</v>
+      </c>
+      <c r="C185" s="71">
+        <v>5.0</v>
+      </c>
+      <c r="D185" s="14">
+        <v>5.16</v>
+      </c>
+      <c r="E185" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="F185" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G185" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="H185" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="I185" s="14" t="s">
+        <v>222</v>
+      </c>
       <c r="J185" s="1"/>
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
     </row>
     <row r="186">
       <c r="A186" s="1"/>
-      <c r="B186" s="34"/>
-      <c r="C186" s="52"/>
-      <c r="D186" s="53"/>
-      <c r="E186" s="34"/>
-      <c r="F186" s="34"/>
-      <c r="G186" s="1"/>
-      <c r="H186" s="1"/>
-      <c r="I186" s="1"/>
+      <c r="B186" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="C186" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="D186" s="14">
+        <v>5.17</v>
+      </c>
+      <c r="E186" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="F186" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G186" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="H186" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="I186" s="14" t="s">
+        <v>225</v>
+      </c>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
       <c r="L186" s="1"/>
     </row>
     <row r="187">
       <c r="A187" s="1"/>
-      <c r="B187" s="34"/>
-      <c r="C187" s="52"/>
-      <c r="D187" s="53"/>
-      <c r="E187" s="34"/>
-      <c r="F187" s="34"/>
-      <c r="G187" s="1"/>
-      <c r="H187" s="1"/>
-      <c r="I187" s="1"/>
+      <c r="B187" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="C187" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="D187" s="14">
+        <v>5.166</v>
+      </c>
+      <c r="E187" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="F187" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G187" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H187" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="I187" s="14" t="s">
+        <v>230</v>
+      </c>
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
       <c r="L187" s="1"/>
@@ -5592,8 +6479,22 @@
       <c r="K224" s="1"/>
       <c r="L224" s="1"/>
     </row>
+    <row r="225">
+      <c r="A225" s="1"/>
+      <c r="B225" s="34"/>
+      <c r="C225" s="52"/>
+      <c r="D225" s="53"/>
+      <c r="E225" s="34"/>
+      <c r="F225" s="34"/>
+      <c r="G225" s="1"/>
+      <c r="H225" s="1"/>
+      <c r="I225" s="1"/>
+      <c r="J225" s="1"/>
+      <c r="K225" s="1"/>
+      <c r="L225" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="21">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B9:E9"/>
@@ -5601,14 +6502,20 @@
     <mergeCell ref="H10:L10"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="H24:L24"/>
-    <mergeCell ref="B100:H100"/>
-    <mergeCell ref="B129:G129"/>
+    <mergeCell ref="B132:G132"/>
+    <mergeCell ref="B142:G142"/>
+    <mergeCell ref="B143:G143"/>
+    <mergeCell ref="B160:I160"/>
+    <mergeCell ref="B161:I161"/>
+    <mergeCell ref="B170:I170"/>
+    <mergeCell ref="B179:I179"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="B57:G57"/>
     <mergeCell ref="B72:G72"/>
     <mergeCell ref="B80:G80"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="E93:F93"/>
+    <mergeCell ref="B100:H100"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Results/Results.xlsx
+++ b/Results/Results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="231">
   <si>
     <t>Protocol Assessment: Compliant vs Rack&amp;Pinion</t>
   </si>
@@ -364,28 +364,28 @@
     <t>Success (%) Compliant</t>
   </si>
   <si>
-    <t>Success (%) R&amp;P</t>
-  </si>
-  <si>
     <t>Damage Compliant (Y/N)</t>
   </si>
   <si>
-    <t>Damage R&amp;P (Y/N)</t>
-  </si>
-  <si>
-    <t>Heavy and rigid (Can)</t>
+    <t>Hard (Cube)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Hard (Screwdriver)</t>
+  </si>
+  <si>
+    <t>Hard (Eraser)</t>
   </si>
   <si>
     <t>Fragile (Plastic cup)</t>
   </si>
   <si>
-    <t>Fragile (Egg)</t>
-  </si>
-  <si>
-    <t>Deformable (Foam ball)</t>
-  </si>
-  <si>
-    <t>Standard cube</t>
+    <t>Fragile (Sponge)</t>
+  </si>
+  <si>
+    <t>Fragile (Blu-tack)</t>
   </si>
   <si>
     <t>TEST  E-TEXTILES</t>
@@ -943,7 +943,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="70">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1124,26 +1124,20 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
@@ -4743,109 +4737,111 @@
       <c r="C134" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="D134" s="64" t="s">
+      <c r="D134" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="E134" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="F134" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="G134" s="63" t="s">
-        <v>68</v>
-      </c>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
-      <c r="K134" s="1"/>
-      <c r="L134" s="1"/>
     </row>
     <row r="135">
       <c r="A135" s="1"/>
-      <c r="B135" s="65" t="s">
-        <v>120</v>
-      </c>
-      <c r="C135" s="66"/>
-      <c r="D135" s="67"/>
-      <c r="E135" s="68"/>
-      <c r="F135" s="68"/>
-      <c r="G135" s="66"/>
+      <c r="B135" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="C135" s="65">
+        <v>100.0</v>
+      </c>
+      <c r="D135" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="E135" s="1"/>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
-      <c r="J135" s="1"/>
-      <c r="K135" s="1"/>
-      <c r="L135" s="1"/>
     </row>
     <row r="136">
       <c r="A136" s="1"/>
-      <c r="B136" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="C136" s="66"/>
-      <c r="D136" s="67"/>
-      <c r="E136" s="68"/>
-      <c r="F136" s="68"/>
-      <c r="G136" s="66"/>
+      <c r="B136" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="C136" s="65">
+        <v>100.0</v>
+      </c>
+      <c r="D136" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
-      <c r="J136" s="1"/>
-      <c r="K136" s="1"/>
-      <c r="L136" s="1"/>
     </row>
     <row r="137">
       <c r="A137" s="1"/>
-      <c r="B137" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="C137" s="66"/>
-      <c r="D137" s="67"/>
-      <c r="E137" s="68"/>
-      <c r="F137" s="68"/>
-      <c r="G137" s="66"/>
+      <c r="B137" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="C137" s="65">
+        <v>100.0</v>
+      </c>
+      <c r="D137" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
-      <c r="J137" s="1"/>
-      <c r="K137" s="1"/>
-      <c r="L137" s="1"/>
     </row>
     <row r="138">
       <c r="A138" s="1"/>
-      <c r="B138" s="65" t="s">
-        <v>123</v>
-      </c>
-      <c r="C138" s="66"/>
-      <c r="D138" s="67"/>
-      <c r="E138" s="68"/>
-      <c r="F138" s="68"/>
-      <c r="G138" s="66"/>
+      <c r="B138" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="C138" s="65">
+        <v>100.0</v>
+      </c>
+      <c r="D138" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="E138" s="1"/>
+      <c r="F138" s="1"/>
+      <c r="G138" s="1"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
-      <c r="J138" s="1"/>
-      <c r="K138" s="1"/>
-      <c r="L138" s="1"/>
     </row>
     <row r="139">
       <c r="A139" s="1"/>
-      <c r="B139" s="65" t="s">
-        <v>124</v>
-      </c>
-      <c r="C139" s="66"/>
-      <c r="D139" s="67"/>
-      <c r="E139" s="68"/>
-      <c r="F139" s="68"/>
-      <c r="G139" s="66"/>
+      <c r="B139" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="C139" s="65">
+        <v>100.0</v>
+      </c>
+      <c r="D139" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
-      <c r="J139" s="1"/>
-      <c r="K139" s="1"/>
-      <c r="L139" s="1"/>
     </row>
     <row r="140">
       <c r="A140" s="1"/>
-      <c r="B140" s="34"/>
-      <c r="C140" s="52"/>
-      <c r="D140" s="53"/>
+      <c r="B140" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C140" s="14">
+        <v>100.0</v>
+      </c>
+      <c r="D140" s="66" t="s">
+        <v>119</v>
+      </c>
       <c r="E140" s="34"/>
       <c r="F140" s="34"/>
       <c r="G140" s="1"/>
@@ -5207,7 +5203,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1"/>
-      <c r="B160" s="69" t="s">
+      <c r="B160" s="67" t="s">
         <v>130</v>
       </c>
       <c r="J160" s="1"/>
@@ -5216,7 +5212,7 @@
     </row>
     <row r="161">
       <c r="A161" s="1"/>
-      <c r="B161" s="69" t="s">
+      <c r="B161" s="67" t="s">
         <v>131</v>
       </c>
       <c r="J161" s="1"/>
@@ -5228,7 +5224,7 @@
       <c r="B162" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C162" s="70" t="s">
+      <c r="C162" s="68" t="s">
         <v>133</v>
       </c>
       <c r="D162" s="8" t="s">
@@ -5378,7 +5374,7 @@
       <c r="B167" s="38">
         <v>5.0</v>
       </c>
-      <c r="C167" s="71">
+      <c r="C167" s="69">
         <v>5.0</v>
       </c>
       <c r="D167" s="14">
@@ -5465,7 +5461,7 @@
     </row>
     <row r="170">
       <c r="A170" s="1"/>
-      <c r="B170" s="69" t="s">
+      <c r="B170" s="67" t="s">
         <v>173</v>
       </c>
       <c r="J170" s="1"/>
@@ -5477,7 +5473,7 @@
       <c r="B171" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C171" s="70" t="s">
+      <c r="C171" s="68" t="s">
         <v>133</v>
       </c>
       <c r="D171" s="8" t="s">
@@ -5627,7 +5623,7 @@
       <c r="B176" s="38">
         <v>5.0</v>
       </c>
-      <c r="C176" s="71">
+      <c r="C176" s="69">
         <v>5.0</v>
       </c>
       <c r="D176" s="14">
@@ -5714,7 +5710,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1"/>
-      <c r="B179" s="69" t="s">
+      <c r="B179" s="67" t="s">
         <v>203</v>
       </c>
       <c r="J179" s="1"/>
@@ -5726,7 +5722,7 @@
       <c r="B180" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C180" s="70" t="s">
+      <c r="C180" s="68" t="s">
         <v>133</v>
       </c>
       <c r="D180" s="8" t="s">
@@ -5876,7 +5872,7 @@
       <c r="B185" s="38">
         <v>5.0</v>
       </c>
-      <c r="C185" s="71">
+      <c r="C185" s="69">
         <v>5.0</v>
       </c>
       <c r="D185" s="14">
